--- a/inbox-dropzone/Grok_clone access.xlsx
+++ b/inbox-dropzone/Grok_clone access.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="30" windowWidth="18855" windowHeight="7185" activeTab="4"/>
+    <workbookView xWindow="240" yWindow="30" windowWidth="18855" windowHeight="7185" firstSheet="3" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="Clone" sheetId="1" r:id="rId1"/>
@@ -12,14 +12,16 @@
     <sheet name="Commit 2" sheetId="4" r:id="rId3"/>
     <sheet name="Key Files" sheetId="3" r:id="rId4"/>
     <sheet name="03Dec25 update files" sheetId="6" r:id="rId5"/>
-    <sheet name="Wolfram" sheetId="5" r:id="rId6"/>
+    <sheet name="04Dec2025 update files" sheetId="7" r:id="rId6"/>
+    <sheet name="Wolfram" sheetId="5" r:id="rId7"/>
+    <sheet name="Source4" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1992" uniqueCount="1832">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2684" uniqueCount="2492">
   <si>
     <t>https://github.com/Daniel8Murphy0007/Star-Magic</t>
   </si>
@@ -11628,6 +11630,2685 @@
         <family val="2"/>
       </rPr>
       <t> 80% noise reduction, 100% scientific value retention</t>
+    </r>
+  </si>
+  <si>
+    <t>✅ PHASE 32 DOCUMENTATION UPDATE COMPLETE</t>
+  </si>
+  <si>
+    <t>Execution Summary:</t>
+  </si>
+  <si>
+    <t>BUILD_INSTRUCTIONS_PERMANENT.md</t>
+  </si>
+  <si>
+    <t>BUILD_STATUS.md</t>
+  </si>
+  <si>
+    <t>WORKSPACE_STATUS_CURRENT.md</t>
+  </si>
+  <si>
+    <t>WORKSPACE_QUICK_REFERENCE.md</t>
+  </si>
+  <si>
+    <t>REPOSITORY_STATUS.md</t>
+  </si>
+  <si>
+    <t>QUICK_START.md</t>
+  </si>
+  <si>
+    <t>EMERGENCY_SESSION_CAPTURE_DEC1_2134.md</t>
+  </si>
+  <si>
+    <t>uqff_tracing.h</t>
+  </si>
+  <si>
+    <t>MAIN_1_CoAnQi_integration_status.json</t>
+  </si>
+  <si>
+    <t>15 files changed, 167 insertions(+), 135 deletions(-)</t>
+  </si>
+  <si>
+    <t>17 objects compressed</t>
+  </si>
+  <si>
+    <t>6.80 KiB transferred @ 2.27 MiB/s</t>
+  </si>
+  <si>
+    <t>Repository Status:</t>
+  </si>
+  <si>
+    <r>
+      <t>✅ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>15 Files Updated:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> All documentation files updated to Phase 32 (Dec 4 @ 18:58)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>✅ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>Git Commit:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 4452a02 - "Phase 32 documentation update: All 15 workspace files updated to Dec 4 @ 18:58 (Qt networking + Virgo Cluster physics integration)"</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>✅ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>Git Push:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> Successfully pushed to origin/master</t>
+    </r>
+  </si>
+  <si>
+    <t>HEAD: 4452a02 (master, origin/master, origin/HEAD)</t>
+  </si>
+  <si>
+    <t>Previous commits:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  5a6346f - Phase 32: Workspace update (CMakeLists, workspace config, Star-Magic.md)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  168711c - Dec 4 session: Qt networking + Virgo Cluster physics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ab1dac9 - Phase 31: CMakeLists.txt fix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ecb8aa6 - Source2 HEAD PROGRAM Complete</t>
+  </si>
+  <si>
+    <t>Remote Sync:</t>
+  </si>
+  <si>
+    <t>✅ Working tree clean (only untracked temp files present)</t>
+  </si>
+  <si>
+    <t>Untracked Files:</t>
+  </si>
+  <si>
+    <t>C++17_MINGW_CONTAMINATION_REPORT.txt</t>
+  </si>
+  <si>
+    <t>SESSION_LOCK_DEC1_2134.md</t>
+  </si>
+  <si>
+    <t>SOURCE82_MERGE_COMPLETION_REPORT.md</t>
+  </si>
+  <si>
+    <t>WORKSPACE_BACKUP_739PM/</t>
+  </si>
+  <si>
+    <t>merge_*.ps1, merge_*.py (source82 merge scripts)</t>
+  </si>
+  <si>
+    <t>source82_wolfram_*.cpp.bak, source82_wolfram_*.txt (temp Virgo work files)</t>
+  </si>
+  <si>
+    <t>All Phase 32 documentation updates complete and pushed to remote. ✅</t>
+  </si>
+  <si>
+    <r>
+      <t>✅ Branch master is </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>up to date with origin/master</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>✅ All Phase 32 changes </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>successfully synced to GitHub</t>
+    </r>
+  </si>
+  <si>
+    <t>✅ ALL UPDATES COMPLETE</t>
+  </si>
+  <si>
+    <t>Workspace Update Summary:</t>
+  </si>
+  <si>
+    <t>1. ✅ Backup Created: MAIN_1_CoAnQi_backup_04dec2025_1858.cpp (103,952 insertions)</t>
+  </si>
+  <si>
+    <t>2. ✅ CMakeLists.txt Updated:</t>
+  </si>
+  <si>
+    <t>Build status: December 4, 2025 - Commit 168711c</t>
+  </si>
+  <si>
+    <t>Executable: 1.35 MB</t>
+  </si>
+  <si>
+    <t>Session: Qt networking + Virgo Cluster physics</t>
+  </si>
+  <si>
+    <t>3. ✅ Star-Magic.code-workspace Updated:</t>
+  </si>
+  <si>
+    <t>Phase 32: Qt Networking + Virgo Cluster Physics Integration</t>
+  </si>
+  <si>
+    <t>Restore point: 168711c</t>
+  </si>
+  <si>
+    <t>Session timestamp: December 4, 2025 @ 18:58:00</t>
+  </si>
+  <si>
+    <t>Updated file size: 1.35 MB</t>
+  </si>
+  <si>
+    <t>4. ✅ Star-Magic.md Updated:</t>
+  </si>
+  <si>
+    <t>Integration status: Dec 4 @ 18:58</t>
+  </si>
+  <si>
+    <t>New features: Qt networking, Virgo Cluster physics</t>
+  </si>
+  <si>
+    <t>Latest commit: 168711c</t>
+  </si>
+  <si>
+    <t>Quick stats table updated</t>
+  </si>
+  <si>
+    <t>5. ✅ SESSION_RESTORE_DEC4_1858.md Created:</t>
+  </si>
+  <si>
+    <t>Complete session restoration point</t>
+  </si>
+  <si>
+    <t>All file modifications documented</t>
+  </si>
+  <si>
+    <t>Git state snapshot</t>
+  </si>
+  <si>
+    <t>Recovery commands included</t>
+  </si>
+  <si>
+    <t>Emergency restoration procedures</t>
+  </si>
+  <si>
+    <t>6. ✅ Git Commit &amp; Push:</t>
+  </si>
+  <si>
+    <t>Commit: 5a6346f - "Phase 32: Workspace update - CMakeLists, workspace config, Star-Magic.md + Dec 4 session restore point"</t>
+  </si>
+  <si>
+    <t>Files changed: 5</t>
+  </si>
+  <si>
+    <t>Pushed to GitHub: origin/master</t>
+  </si>
+  <si>
+    <r>
+      <t>Current Position:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> HEAD at 5a6346f, all workspace files synchronized and backed up.</t>
+    </r>
+  </si>
+  <si>
+    <t>SOURCE4 INTEGRATION PLAN FOR MAIN_1_CoAnQi.cpp</t>
+  </si>
+  <si>
+    <t>EXECUTIVE SUMMARY</t>
+  </si>
+  <si>
+    <t>PHYSICS INVENTORY - SOURCE4 SIMULTANEOUS SOLVER SYSTEM</t>
+  </si>
+  <si>
+    <t>1. UNIFIED FIELD THEORY (UQFF) - 8 Components</t>
+  </si>
+  <si>
+    <r>
+      <t>Integration Scope:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 46 PhysicsTerm classes + 37 compute functions + 7 astrophysical systems + Navier-Stokes fluid solver</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Total Physics:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> Unified Field Theory (UQFF) + MUGE Compressed + MUGE Resonance + Fluid Dynamics</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Integration Method:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> SOURCE4 block insertion (similar to SOURCE1-116 pattern)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Estimated Lines:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> ~2,100 lines (source4.cpp: 1782 + wolfram classes: ~350 unique)</t>
+    </r>
+  </si>
+  <si>
+    <t>FU = Ug1 + Ug2 + Ug3 + Ug4 + Ubi + Um + A_μν</t>
+  </si>
+  <si>
+    <t>Component</t>
+  </si>
+  <si>
+    <t>Physics</t>
+  </si>
+  <si>
+    <t>Equation Form</t>
+  </si>
+  <si>
+    <t>Implementation</t>
+  </si>
+  <si>
+    <t>Ug1</t>
+  </si>
+  <si>
+    <t>Magnetic dipole-gradient gravity</t>
+  </si>
+  <si>
+    <t>k1*μ_s*∇(M/r)*exp(-αt)*cos(πt_n)*defect</t>
+  </si>
+  <si>
+    <t>compute_Ug1() + UniversalGravity1Term</t>
+  </si>
+  <si>
+    <t>Ug2</t>
+  </si>
+  <si>
+    <t>Charge-reactivity gravity</t>
+  </si>
+  <si>
+    <t>k2*(Q_A+Q_UA)*M/r²*S*wind*H_SCm*E_react</t>
+  </si>
+  <si>
+    <t>compute_Ug2() + UniversalGravity2Term</t>
+  </si>
+  <si>
+    <t>Ug3</t>
+  </si>
+  <si>
+    <t>Magnetic string rotation</t>
+  </si>
+  <si>
+    <t>k3*B_j*cos(ω_s(t)*π*t)*P_core*E_react</t>
+  </si>
+  <si>
+    <t>compute_Ug3() + UniversalGravity3Term</t>
+  </si>
+  <si>
+    <t>Ug4</t>
+  </si>
+  <si>
+    <t>Vacuum energy concentration</t>
+  </si>
+  <si>
+    <t>k4*ρ_v*C*M_bh/d_g²*exp(-αt_n)*f_feedback</t>
+  </si>
+  <si>
+    <t>compute_Ug4() + UniversalGravity4Term</t>
+  </si>
+  <si>
+    <t>U_bi</t>
+  </si>
+  <si>
+    <t>Universal buoyancy</t>
+  </si>
+  <si>
+    <t>β_i*Σ(Ug_i)*(1+Ω_g*M_bh/d_g)*SW*U_UA*cos(πt_n)</t>
+  </si>
+  <si>
+    <t>compute_Ubi() + UniversalBuoyancyTerm</t>
+  </si>
+  <si>
+    <t>U_m</t>
+  </si>
+  <si>
+    <t>Universal magnetism</t>
+  </si>
+  <si>
+    <t>Σ_j[γ*μ_j*exp(-γt_n)*E_react*φ̂_j]</t>
+  </si>
+  <si>
+    <t>compute_Um() + UniversalMagnetismTerm</t>
+  </si>
+  <si>
+    <t>A_μν</t>
+  </si>
+  <si>
+    <t>Cosmic aether metric</t>
+  </si>
+  <si>
+    <t>η*T_s00*[δ_μν - interaction]</t>
+  </si>
+  <si>
+    <t>compute_A_mu_nu() + UniversalAetherTerm</t>
+  </si>
+  <si>
+    <t>FU</t>
+  </si>
+  <si>
+    <t>Complete unified field</t>
+  </si>
+  <si>
+    <t>FU = Σ(all components)</t>
+  </si>
+  <si>
+    <t>compute_FU() + UnifiedFieldTerm</t>
+  </si>
+  <si>
+    <t>Helper Functions (6):</t>
+  </si>
+  <si>
+    <t>compute_Ereact() - Reactor efficiency: (ρ_SCm*v²_SCm/ρ_A)*exp(-κt) → ReactorEfficiencyTerm</t>
+  </si>
+  <si>
+    <t>compute_mu_s() - Magnetic dipole: B_s(t)*R³_s → MuSTerm</t>
+  </si>
+  <si>
+    <t>compute_grad_Ms_r() - Surface gravity: G*M_s/R²_s → GradMsRTerm</t>
+  </si>
+  <si>
+    <t>compute_Bj() - String field: 10⁻³ + 0.4*sin(ω_c*t) + SCm → BjTerm</t>
+  </si>
+  <si>
+    <t>compute_omega_s_t() - Rotation frequency: ω_s - 0.4e-6*sin(ω_c*t) → OmegaSTTerm</t>
+  </si>
+  <si>
+    <t>compute_mu_j() - String dipole: B_j(t)*R³_s → MuJTerm</t>
+  </si>
+  <si>
+    <t>2. MUGE COMPRESSED EQUATION - 9 Components</t>
+  </si>
+  <si>
+    <t>g_compressed = base * expansion * super_adj * envelope + Ug_sum + cosm + quantum + fluid + perturbation</t>
+  </si>
+  <si>
+    <t>Formula</t>
+  </si>
+  <si>
+    <t>Base</t>
+  </si>
+  <si>
+    <t>Newtonian gravity</t>
+  </si>
+  <si>
+    <t>G*M/r²</t>
+  </si>
+  <si>
+    <t>compute_compressed_base() + MUGECompressedBaseTerm</t>
+  </si>
+  <si>
+    <t>Expansion</t>
+  </si>
+  <si>
+    <t>Hubble modulation</t>
+  </si>
+  <si>
+    <t>1 + H₀*t</t>
+  </si>
+  <si>
+    <t>compute_compressed_expansion() + MUGEExpansionTerm</t>
+  </si>
+  <si>
+    <t>Super Adj</t>
+  </si>
+  <si>
+    <t>Magnetic suppression</t>
+  </si>
+  <si>
+    <t>1 - B/B_crit</t>
+  </si>
+  <si>
+    <t>compute_compressed_super_adj() + MUGESuperAdjustmentTerm</t>
+  </si>
+  <si>
+    <t>Envelope</t>
+  </si>
+  <si>
+    <t>Placeholder</t>
+  </si>
+  <si>
+    <t>compute_compressed_env() + MUGEEnvelopeTerm</t>
+  </si>
+  <si>
+    <t>Ug Sum</t>
+  </si>
+  <si>
+    <t>Unified gravity sum</t>
+  </si>
+  <si>
+    <t>Σ(Ug1-4)</t>
+  </si>
+  <si>
+    <t>compute_compressed_Ug_sum() + MUGEUgSumTerm</t>
+  </si>
+  <si>
+    <t>Cosmological</t>
+  </si>
+  <si>
+    <t>Dark energy</t>
+  </si>
+  <si>
+    <t>Λc²/3</t>
+  </si>
+  <si>
+    <t>compute_compressed_cosm() + MUGECosmologicalTerm</t>
+  </si>
+  <si>
+    <t>Quantum</t>
+  </si>
+  <si>
+    <t>Uncertainty principle</t>
+  </si>
+  <si>
+    <t>ℏ*Δx_p*∫ψ*ψ/(πt_H)</t>
+  </si>
+  <si>
+    <t>compute_compressed_quantum() + MUGEQuantumTerm</t>
+  </si>
+  <si>
+    <t>Fluid</t>
+  </si>
+  <si>
+    <t>Navier-Stokes coupling</t>
+  </si>
+  <si>
+    <t>ρ_fluid*V_sys*g_local</t>
+  </si>
+  <si>
+    <t>compute_compressed_fluid() + MUGEFluidTerm</t>
+  </si>
+  <si>
+    <t>Perturbation</t>
+  </si>
+  <si>
+    <t>Dark matter</t>
+  </si>
+  <si>
+    <t>G*(M+M_DM)*(1+δρ/ρ)/r²</t>
+  </si>
+  <si>
+    <t>compute_compressed_pert() + MUGEPerturbationTerm</t>
+  </si>
+  <si>
+    <t>Total Function: compute_compressed_MUGE(MUGESystem) + CompressedMUGETerm (monolithic wrapper)</t>
+  </si>
+  <si>
+    <t>3. MUGE RESONANCE EQUATION - 13 Components + Wormhole</t>
+  </si>
+  <si>
+    <t xml:space="preserve">g_resonance = aDPM + aTHz + Avac_diff + aSuperFreq + aAetherRes + Ug4_i </t>
+  </si>
+  <si>
+    <t xml:space="preserve">            + aQuantumFreq + aAetherFreq + aFluidFreq + oscillatory </t>
+  </si>
+  <si>
+    <t xml:space="preserve">            + aExpFreq + fTRZ + wormhole</t>
+  </si>
+  <si>
+    <t>aDPM</t>
+  </si>
+  <si>
+    <t>Base DPM acceleration</t>
+  </si>
+  <si>
+    <t>F_DPM*f_DPM*E_vac_neb*c_res*V_sys</t>
+  </si>
+  <si>
+    <t>compute_resonance_aDPM() + MUGEResonanceADPMTerm</t>
+  </si>
+  <si>
+    <t>aTHz</t>
+  </si>
+  <si>
+    <t>THz frequency</t>
+  </si>
+  <si>
+    <t>f_THz*E_vac_neb*v_exp*aDPM/(E_vac_ISM*c_res)</t>
+  </si>
+  <si>
+    <t>compute_resonance_aTHz() + MUGEResonanceATHzTerm</t>
+  </si>
+  <si>
+    <t>Avac_diff</t>
+  </si>
+  <si>
+    <t>Vacuum differential</t>
+  </si>
+  <si>
+    <t>ΔE_vac*f_DPM*cos(ω_i*t)</t>
+  </si>
+  <si>
+    <t>compute_resonance_Avac_diff() + MUGEResonanceAvacDiffTerm</t>
+  </si>
+  <si>
+    <t>aSuperFreq</t>
+  </si>
+  <si>
+    <t>Superconductive resonance</t>
+  </si>
+  <si>
+    <t>F_super*UA_SCM*aDPM</t>
+  </si>
+  <si>
+    <t>compute_resonance_aSuperFreq() + MUGEResonanceASuperFreqTerm</t>
+  </si>
+  <si>
+    <t>aAetherRes</t>
+  </si>
+  <si>
+    <t>Aether coupling</t>
+  </si>
+  <si>
+    <t>aDPM*UA_SCM*Avac_diff</t>
+  </si>
+  <si>
+    <t>compute_resonance_aAetherRes() + MUGEResonanceAAetherResTerm</t>
+  </si>
+  <si>
+    <t>Ug4_i</t>
+  </si>
+  <si>
+    <t>Reactor gravity</t>
+  </si>
+  <si>
+    <t>k4_res*f_react*aDPM*cos(ω_i*t)</t>
+  </si>
+  <si>
+    <t>compute_resonance_Ug4_i() + MUGEResonanceUg4iTerm</t>
+  </si>
+  <si>
+    <t>aQuantumFreq</t>
+  </si>
+  <si>
+    <t>Quantum frequency</t>
+  </si>
+  <si>
+    <t>f_quantum*aDPM</t>
+  </si>
+  <si>
+    <t>compute_resonance_aQuantumFreq() + MUGEResonanceAQuantumFreqTerm</t>
+  </si>
+  <si>
+    <t>aAetherFreq</t>
+  </si>
+  <si>
+    <t>Aether frequency</t>
+  </si>
+  <si>
+    <t>f_Aether*aDPM</t>
+  </si>
+  <si>
+    <t>compute_resonance_aAetherFreq() + MUGEResonanceAAetherFreqTerm</t>
+  </si>
+  <si>
+    <t>aFluidFreq</t>
+  </si>
+  <si>
+    <t>Fluid frequency</t>
+  </si>
+  <si>
+    <t>f_fluid*aDPM</t>
+  </si>
+  <si>
+    <t>compute_resonance_aFluidFreq() + MUGEResonanceAFluidFreqTerm</t>
+  </si>
+  <si>
+    <t>Oscillatory</t>
+  </si>
+  <si>
+    <t>Simplified oscillation</t>
+  </si>
+  <si>
+    <t>aDPM*cos(ω_i*t)</t>
+  </si>
+  <si>
+    <t>compute_resonance_osc() + MUGEResonanceOscTerm</t>
+  </si>
+  <si>
+    <t>aExpFreq</t>
+  </si>
+  <si>
+    <t>Expansion frequency</t>
+  </si>
+  <si>
+    <t>aDPM*aTHz*f_TRZ*c_res*H₀*t_sys</t>
+  </si>
+  <si>
+    <t>compute_resonance_aExpFreq() + MUGEResonanceAExpFreqTerm</t>
+  </si>
+  <si>
+    <t>fTRZ</t>
+  </si>
+  <si>
+    <t>TRZ factor</t>
+  </si>
+  <si>
+    <t>f_TRZ</t>
+  </si>
+  <si>
+    <t>(included in aExpFreq) + MUGEResonanceFTRZTerm</t>
+  </si>
+  <si>
+    <t>Wormhole</t>
+  </si>
+  <si>
+    <t>Metric contribution</t>
+  </si>
+  <si>
+    <t>(1 - b/r)*f_worm</t>
+  </si>
+  <si>
+    <t>compute_resonance_wormhole() + MUGEResonanceWormholeTerm</t>
+  </si>
+  <si>
+    <t>Total Function: compute_resonance_MUGE(MUGESystem, ResonanceParams) + ResonanceMUGETerm (monolithic wrapper)</t>
+  </si>
+  <si>
+    <t>4. NAVIER-STOKES FLUID SOLVER</t>
+  </si>
+  <si>
+    <t>FluidSolver class (Jos Stam's Stable Fluids method)</t>
+  </si>
+  <si>
+    <t>- 2D incompressible flow on N×N grid</t>
+  </si>
+  <si>
+    <t>- Quasar jet simulation (J1610+1811 parameters)</t>
+  </si>
+  <si>
+    <t>- UQFF force coupling via MUGE g</t>
+  </si>
+  <si>
+    <t>Methods:</t>
+  </si>
+  <si>
+    <t>diffuse() - Viscosity diffusion</t>
+  </si>
+  <si>
+    <t>advect() - Self-advection</t>
+  </si>
+  <si>
+    <t>project() - Incompressibility projection</t>
+  </si>
+  <si>
+    <t>step() - Complete timestep with UQFF forcing</t>
+  </si>
+  <si>
+    <t>simulate_quasar_jet() - Relativistic jet (v_SCm = 0.99c)</t>
+  </si>
+  <si>
+    <t>5. ASTROPHYSICAL SYSTEMS (7 Systems)</t>
+  </si>
+  <si>
+    <t>System</t>
+  </si>
+  <si>
+    <t>Parameters</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>SGR1745</t>
+  </si>
+  <si>
+    <t>M=2.984e30 kg, B=1e10 T, z=0.0009</t>
+  </si>
+  <si>
+    <t>Magnetar near Sgr A*</t>
+  </si>
+  <si>
+    <t>M=8.155e36 kg, M_DM=1e37 kg</t>
+  </si>
+  <si>
+    <t>Galactic center SMBH</t>
+  </si>
+  <si>
+    <t>Tapestry</t>
+  </si>
+  <si>
+    <t>M=1.989e35 kg, V_sys=1e53 m³</t>
+  </si>
+  <si>
+    <t>Star formation region</t>
+  </si>
+  <si>
+    <t>Westerlund2</t>
+  </si>
+  <si>
+    <t>M=1e37 kg, z=0.002</t>
+  </si>
+  <si>
+    <t>Young massive cluster</t>
+  </si>
+  <si>
+    <t>Pillars of Creation</t>
+  </si>
+  <si>
+    <t>M=1.989e32 kg, r=9.46e15 m</t>
+  </si>
+  <si>
+    <t>M16 star-forming pillars</t>
+  </si>
+  <si>
+    <t>Rings of Relativity</t>
+  </si>
+  <si>
+    <t>M=1.989e36 kg, z=0.01</t>
+  </si>
+  <si>
+    <t>Gravitational lensing system</t>
+  </si>
+  <si>
+    <t>Student Guide Universe</t>
+  </si>
+  <si>
+    <t>M=1e53 kg, r=1e26 m</t>
+  </si>
+  <si>
+    <t>Cosmological scale</t>
+  </si>
+  <si>
+    <t>Each system has PhysicsTerm class in source4_wolfram.cpp</t>
+  </si>
+  <si>
+    <t>INTEGRATION ARCHITECTURE</t>
+  </si>
+  <si>
+    <t>File Structure Analysis</t>
+  </si>
+  <si>
+    <t>File</t>
+  </si>
+  <si>
+    <t>Lines</t>
+  </si>
+  <si>
+    <t>Classes</t>
+  </si>
+  <si>
+    <t>Functions</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>source4.cpp</t>
+  </si>
+  <si>
+    <t>2 base + CelestialBody + MUGESystem + ResonanceParams</t>
+  </si>
+  <si>
+    <t>37 compute_*</t>
+  </si>
+  <si>
+    <t>COMPLETE</t>
+  </si>
+  <si>
+    <t>source4_wolfram.cpp</t>
+  </si>
+  <si>
+    <t>24 (8 UQFF + 2 monolithic MUGE + 7 systems + 6 helpers + util)</t>
+  </si>
+  <si>
+    <t>PHASE 1 ✅</t>
+  </si>
+  <si>
+    <t>source4_wolfram_compressed.cpp</t>
+  </si>
+  <si>
+    <t>9 (MUGE compressed components)</t>
+  </si>
+  <si>
+    <t>1 registration</t>
+  </si>
+  <si>
+    <t>PHASE 2 ✅</t>
+  </si>
+  <si>
+    <t>source4_wolfram_resonance.cpp</t>
+  </si>
+  <si>
+    <t>13 (MUGE resonance components)</t>
+  </si>
+  <si>
+    <t>COMPLETE ✅</t>
+  </si>
+  <si>
+    <t>CRITICAL ISSUE: PhysicsTerm REDEFINITION CONFLICT</t>
+  </si>
+  <si>
+    <t>Problem: PhysicsTerm base class defined in 4 different files:</t>
+  </si>
+  <si>
+    <t>1. source4.cpp (line 48) - ORIGINAL DEFINITION</t>
+  </si>
+  <si>
+    <t>2. source4_wolfram.cpp (implicit - inherits from external)</t>
+  </si>
+  <si>
+    <t>3. source4_wolfram_compressed.cpp (NO definition - assumes external)</t>
+  </si>
+  <si>
+    <t>4. source4_wolfram_resonance.cpp (line 17) - REDEFINITION</t>
+  </si>
+  <si>
+    <t>Solution Strategy:</t>
+  </si>
+  <si>
+    <t>Define ONCE in MAIN_1_CoAnQi.cpp (already exists at line 199)</t>
+  </si>
+  <si>
+    <t>Use #ifndef guards if keeping source4.cpp standalone capability</t>
+  </si>
+  <si>
+    <t>INTEGRATION PLAN: 5-PHASE APPROACH</t>
+  </si>
+  <si>
+    <t>PHASE 1: CONSOLIDATE BASE CLASSES (Pre-Integration)</t>
+  </si>
+  <si>
+    <t>Step 1.1: Verify PhysicsTerm in MAIN_1_CoAnQi.cpp</t>
+  </si>
+  <si>
+    <r>
+      <t>add_source()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> - Source term injection</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SagittariusA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>*</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Total Classes:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 46 PhysicsTerm subclasses + 3 data structures</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Total Functions:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 37 compute_* functions + 3 registration functions</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Impact:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> Cannot compile all files together without linker errors</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Remove ALL redefinitions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> in source4 files</t>
+    </r>
+  </si>
+  <si>
+    <t>// Line 199-228: PhysicsTerm base class (ALREADY EXISTS)</t>
+  </si>
+  <si>
+    <t>class PhysicsTerm {</t>
+  </si>
+  <si>
+    <t>public:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    virtual ~PhysicsTerm() = default;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    virtual double compute(double t, const std::map&lt;std::string, double&gt;&amp; params) const = 0;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    virtual std::string getName() const = 0;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    virtual std::string getDescription() const = 0;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    virtual bool validate(const std::map&lt;std::string, double&gt;&amp; params) const = 0;</t>
+  </si>
+  <si>
+    <t>};</t>
+  </si>
+  <si>
+    <r>
+      <t>✅ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>ACTION:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> None needed - base class exists and matches source4 interface</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Step 1.2:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> Extract Data Structures from C:\Users\tmsjd\source\repos\Daniel8Murphy0007\Star-Magic\source4.cpp</t>
+    </r>
+  </si>
+  <si>
+    <t>// CelestialBody struct (source4.cpp line 177-191)</t>
+  </si>
+  <si>
+    <t>struct CelestialBody {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    std::string name;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    double Ms, Rs, Rb, Ts_surface, omega_s;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    double Bs_avg, SCm_density, QUA, Pcore, PSCm, omega_c;</t>
+  </si>
+  <si>
+    <t>// MUGESystem struct (source4.cpp line 954-976)</t>
+  </si>
+  <si>
+    <t>struct MUGESystem {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    double M, r, t_sys, B, Bcrit, rho_fluid, Vsys;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    double g_local, M_DM, delta_rho_rho, z;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Resonance-specific</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    double vexp, Evac_neb, Evac_ISM, Delta_Evac;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    double I, A, omega1, omega2, b, f_worm;</t>
+  </si>
+  <si>
+    <t>// ResonanceParams struct (source4.cpp line 928-952)</t>
+  </si>
+  <si>
+    <t>struct ResonanceParams {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    double fDPM, fTHz, Fsuper, UA_SCM, omega_i;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    double k4_res, fquantum, fAether, ffluid, freact;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    double fTRZ, c_res;</t>
+  </si>
+  <si>
+    <t>✅ ACTION: Insert after PhysicsTerm definition in MAIN_1_CoAnQi.cpp</t>
+  </si>
+  <si>
+    <t>PHASE 2: INSERT SOURCE4 BLOCK INTO MAIN_1_CoAnQi.cpp</t>
+  </si>
+  <si>
+    <t>Block Structure:</t>
+  </si>
+  <si>
+    <r>
+      <t>Location:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> After SOURCE116 (currently line 25623), before SOURCE82 (line 25624)</t>
+    </r>
+  </si>
+  <si>
+    <t>// ============================================================================</t>
+  </si>
+  <si>
+    <t>// SOURCE4: UNIFIED FIELD THEORY (UQFF + MUGE COMPRESSED + MUGE RESONANCE)</t>
+  </si>
+  <si>
+    <t>// Integrated: December 5, 2025</t>
+  </si>
+  <si>
+    <t>// Origin: source4.cpp (1782 lines) + source4_wolfram*.cpp (1810 lines)</t>
+  </si>
+  <si>
+    <t>// Total Classes: 46 PhysicsTerm subclasses</t>
+  </si>
+  <si>
+    <t>// Total Functions: 37 compute_* functions + FluidSolver</t>
+  </si>
+  <si>
+    <t>// Physics: 8 UQFF components + 9 MUGE compressed + 13 MUGE resonance + 7 systems</t>
+  </si>
+  <si>
+    <t>// PART A: CONSTANTS AND GLOBALS (source4.cpp lines 136-200)</t>
+  </si>
+  <si>
+    <t>namespace SOURCE4 {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Physical constants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    const double PI = 3.141592653589793;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    const double c = 3.0e8;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    const double G = 6.67430e-11;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    const double H0 = 2.269e-18;  // Hubble constant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    const double Lambda = 1.1e-52; // Cosmological constant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    const double hbar = 1.0546e-34; // Reduced Planck constant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Galactic parameters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    double Omega_g = 7.3e-16;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    double Mbh = 8.15e36;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    double dg = 2.55e20;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // SCm/Aether parameters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    double v_SCm = 0.99 * c;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    double rho_A = 1e-23;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    double rho_sw = 8e-21;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    double v_sw = 5e5;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    double QA = 1e-10;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    double Qs = 0.0;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    double kappa = 0.0005;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    double alpha = 0.001;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    double gamma = 0.00005;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // ... (all 30+ parameters from source4.cpp)</t>
+  </si>
+  <si>
+    <t>}</t>
+  </si>
+  <si>
+    <t>// PART B: DATA STRUCTURES (3 structs)</t>
+  </si>
+  <si>
+    <t>// CelestialBody, MUGESystem, ResonanceParams</t>
+  </si>
+  <si>
+    <t>// PART C: HELPER FUNCTION CLASSES (6 classes from source4_wolfram.cpp)</t>
+  </si>
+  <si>
+    <t>// ReactorEfficiencyTerm, MuSTerm, GradMsRTerm, BjTerm, OmegaSTTerm, MuJTerm</t>
+  </si>
+  <si>
+    <t>// PART D: UNIFIED FIELD CLASSES (8 classes)</t>
+  </si>
+  <si>
+    <t>// UniversalGravity1-4Term, UniversalBuoyancyTerm, UniversalMagnetismTerm</t>
+  </si>
+  <si>
+    <t>// UniversalAetherTerm, UnifiedFieldTerm</t>
+  </si>
+  <si>
+    <t>// PART E: MUGE COMPRESSED CLASSES (9 classes from source4_wolfram_compressed.cpp)</t>
+  </si>
+  <si>
+    <t>// MUGECompressedBaseTerm, MUGEExpansionTerm, MUGESuperAdjustmentTerm, etc.</t>
+  </si>
+  <si>
+    <t>// PART F: MUGE RESONANCE CLASSES (13 classes from source4_wolfram_resonance.cpp)</t>
+  </si>
+  <si>
+    <t>// MUGEResonanceADPMTerm, MUGEResonanceATHzTerm, etc.</t>
+  </si>
+  <si>
+    <t>// PART G: ASTROPHYSICAL SYSTEM CLASSES (7 classes)</t>
+  </si>
+  <si>
+    <t>// SGR1745MagnetarTerm, SagittariusAStarTerm, etc.</t>
+  </si>
+  <si>
+    <t>// PART H: COMPUTE FUNCTIONS (37 functions from source4.cpp)</t>
+  </si>
+  <si>
+    <t>// compute_Ereact(), compute_mu_s(), compute_Ug1-4(), compute_FU()</t>
+  </si>
+  <si>
+    <t>// compute_compressed_MUGE(), compute_resonance_MUGE()</t>
+  </si>
+  <si>
+    <t>// PART I: NAVIER-STOKES FLUID SOLVER (FluidSolver class)</t>
+  </si>
+  <si>
+    <t>// Jos Stam's Stable Fluids method + UQFF force coupling</t>
+  </si>
+  <si>
+    <t>// PART J: SYSTEM INSTANTIATION (7 global MUGESystem objects)</t>
+  </si>
+  <si>
+    <t>// sgr1745, sagA, tapestry, westerlund, pillars, rings, student_guide</t>
+  </si>
+  <si>
+    <t>} // End SOURCE4 block</t>
+  </si>
+  <si>
+    <t>PHASE 3: RESOLVE COMPILATION CONFLICTS</t>
+  </si>
+  <si>
+    <t>Issue 1: PhysicsTerm Redefinition</t>
+  </si>
+  <si>
+    <t>✅ Use existing PhysicsTerm from MAIN_1_CoAnQi.cpp (line 199)</t>
+  </si>
+  <si>
+    <t>❌ Remove class PhysicsTerm from source4_wolfram_resonance.cpp before copy</t>
+  </si>
+  <si>
+    <t>✅ All classes inherit from global PhysicsTerm</t>
+  </si>
+  <si>
+    <t>Issue 2: Constant Redefinition</t>
+  </si>
+  <si>
+    <t>✅ Reference as SOURCE4::PI, SOURCE4::c, etc.</t>
+  </si>
+  <si>
+    <t>✅ Prevents collision with global constants or other SOURCE blocks</t>
+  </si>
+  <si>
+    <t>Issue 3: Function Name Collisions</t>
+  </si>
+  <si>
+    <t>❌ AVOID: Global compute_Ug1() conflicts with SOURCE85 NGC346 module</t>
+  </si>
+  <si>
+    <t>✅ Reference as SOURCE4::compute_Ug1()</t>
+  </si>
+  <si>
+    <t>Issue 4: FluidSolver Class</t>
+  </si>
+  <si>
+    <t>✅ Use #define IX(i,j) macro locally (already scoped)</t>
+  </si>
+  <si>
+    <t>❌ May conflict with other fluid solvers if extracted</t>
+  </si>
+  <si>
+    <t>Issue 5: Global System Objects</t>
+  </si>
+  <si>
+    <t>Example: static MUGESystem SOURCE4::sgr1745 = { ... };</t>
+  </si>
+  <si>
+    <t>PHASE 4: MODULAR EXTRACTION AND INSERTION</t>
+  </si>
+  <si>
+    <t>Step 4.1: Extract from source4.cpp (1782 lines)</t>
+  </si>
+  <si>
+    <r>
+      <t>Estimated Lines:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 2,100 lines total</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>✅ Wrap all constants in </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>namespace SOURCE4 { }</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>✅ Wrap all compute_* functions in </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>namespace SOURCE4 { }</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>✅ Keep in </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>namespace SOURCE4 { }</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>✅ Wrap in </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>namespace SOURCE4 { }</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>✅ Declare as </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>static</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> to prevent external linkage</t>
+    </r>
+  </si>
+  <si>
+    <t>Lines 136-200:   Constants (65 lines) → PART A</t>
+  </si>
+  <si>
+    <t>Lines 177-191:   CelestialBody struct (15 lines) → PART B</t>
+  </si>
+  <si>
+    <t>Lines 954-976:   MUGESystem struct (23 lines) → PART B</t>
+  </si>
+  <si>
+    <t>Lines 928-952:   ResonanceParams struct (25 lines) → PART B</t>
+  </si>
+  <si>
+    <t>Lines 202-239:   Helper functions (38 lines) → PART H</t>
+  </si>
+  <si>
+    <t>Lines 240-299:   UQFF compute functions (60 lines) → PART H</t>
+  </si>
+  <si>
+    <t>Lines 1024-1095: MUGE compressed functions (72 lines) → PART H</t>
+  </si>
+  <si>
+    <t>Lines 1097-1183: MUGE resonance functions (87 lines) → PART H</t>
+  </si>
+  <si>
+    <t>Lines 322-923:   FluidSolver class (602 lines) → PART I</t>
+  </si>
+  <si>
+    <t>Lines 979-1021: System definitions (43 lines) → PART J</t>
+  </si>
+  <si>
+    <t>Step 4.2: Extract from source4_wolfram.cpp (870 lines)</t>
+  </si>
+  <si>
+    <t>Lines 15-106:    UniversalGravity1-3Term (92 lines) → PART D</t>
+  </si>
+  <si>
+    <t>Lines 107-141:   UniversalGravity4Term (35 lines) → PART D</t>
+  </si>
+  <si>
+    <t>Lines 143-175:   UniversalBuoyancyTerm (33 lines) → PART D</t>
+  </si>
+  <si>
+    <t>Lines 177-208:   UniversalMagnetismTerm (32 lines) → PART D</t>
+  </si>
+  <si>
+    <t>Lines 210-232:   UniversalAetherTerm (23 lines) → PART D</t>
+  </si>
+  <si>
+    <t>Lines 234-262:   UnifiedFieldTerm (29 lines) → PART D</t>
+  </si>
+  <si>
+    <t>Lines 642-773:   Helper terms (132 lines) → PART C</t>
+  </si>
+  <si>
+    <t>Lines 447-637:   System terms (191 lines) → PART G</t>
+  </si>
+  <si>
+    <t>Step 4.3: Extract from source4_wolfram_compressed.cpp (312 lines)</t>
+  </si>
+  <si>
+    <t>Lines 19-234:    All 9 MUGE compressed classes (216 lines) → PART E</t>
+  </si>
+  <si>
+    <t>Step 4.4: Extract from source4_wolfram_resonance.cpp (628 lines)</t>
+  </si>
+  <si>
+    <t>Lines 30-458:    All 13 MUGE resonance classes (429 lines) → PART F</t>
+  </si>
+  <si>
+    <t>SKIP line 17:    PhysicsTerm redefinition (use existing)</t>
+  </si>
+  <si>
+    <t>PHASE 5: VALIDATION AND TESTING</t>
+  </si>
+  <si>
+    <t>Step 5.1: Compilation Test</t>
+  </si>
+  <si>
+    <r>
+      <t>Total Extraction:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> ~2,090 lines</t>
+    </r>
+  </si>
+  <si>
+    <t>cmake --build build_msvc --config Release --target MAIN_1_CoAnQi</t>
+  </si>
+  <si>
+    <t>Expected Warnings:</t>
+  </si>
+  <si>
+    <t>Unused variable warnings (many parameters for future expansion)</t>
+  </si>
+  <si>
+    <t>Potential narrowing conversions (int → double)</t>
+  </si>
+  <si>
+    <t>Critical Errors to Watch:</t>
+  </si>
+  <si>
+    <t>❌ PhysicsTerm redefinition (should be resolved)</t>
+  </si>
+  <si>
+    <t>❌ Multiple definition of constants (should be in namespace)</t>
+  </si>
+  <si>
+    <t>❌ IX macro redefinition (scoped to FluidSolver)</t>
+  </si>
+  <si>
+    <t>Step 5.2: Functional Validation</t>
+  </si>
+  <si>
+    <t>// Add to MAIN_1_CoAnQi.cpp main() menu option (new option 13)</t>
+  </si>
+  <si>
+    <t>case 13: {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    std::cout &lt;&lt; "\n=== SOURCE4 UNIFIED FIELD VALIDATION ===" &lt;&lt; std::endl;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Test CelestialBody UQFF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    SOURCE4::CelestialBody sun = {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "Sun", 1.989e30, 6.96e8, 1.496e13, 5778.0, 2.5e-6,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        1e-4, 1e15, 1e-11, 1.0, 1.0, 2*SOURCE4::PI/(11*365.25*86400)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    };</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    double FU = SOURCE4::compute_FU(sun, 1e13, 0.0, 0.0, 0.0);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    std::cout &lt;&lt; "Sun FU: " &lt;&lt; FU &lt;&lt; " (normalized units)" &lt;&lt; std::endl;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Test MUGE systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    double g_compressed = SOURCE4::compute_compressed_MUGE(SOURCE4::sgr1745);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    double g_resonance = SOURCE4::compute_resonance_MUGE(SOURCE4::sgr1745, SOURCE4::res_params);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    std::cout &lt;&lt; "SGR1745 Compressed: " &lt;&lt; g_compressed &lt;&lt; " m/s²" &lt;&lt; std::endl;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    std::cout &lt;&lt; "SGR1745 Resonance: " &lt;&lt; g_resonance &lt;&lt; " m/s²" &lt;&lt; std::endl;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Test PhysicsTerm classes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    SOURCE4::UniversalGravity1Term ug1;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    std::map&lt;std::string, double&gt; params = {{"mu_s", 1e20}, {"grad_Ms_r", 1e-5}, {"tn", 0.0}};</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    double ug1_val = ug1.compute(0.0, params);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    std::cout &lt;&lt; "UniversalGravity1 test: " &lt;&lt; ug1_val &lt;&lt; std::endl;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    break;</t>
+  </si>
+  <si>
+    <t>Step 5.3: Build Metrics</t>
+  </si>
+  <si>
+    <t>Pre-integration:  MAIN_1_CoAnQi.cpp = 104,241 lines</t>
+  </si>
+  <si>
+    <t>Post-integration: MAIN_1_CoAnQi.cpp = 106,341 lines (+2,100)</t>
+  </si>
+  <si>
+    <t>Exe size:         1.44 MB → ~1.50 MB (+60 KB before UPX)</t>
+  </si>
+  <si>
+    <t>Compressed:       1.44 MB → ~1.48 MB (+40 KB after UPX)</t>
+  </si>
+  <si>
+    <t>SIMULTANEOUS SOLVER INTEGRATION POINTS</t>
+  </si>
+  <si>
+    <t>Cross-Module Communication Strategy</t>
+  </si>
+  <si>
+    <t>Scenario 1: UQFF → MUGE Coupling</t>
+  </si>
+  <si>
+    <t>// Ug1-4 computed individually</t>
+  </si>
+  <si>
+    <t>double Ug1 = SOURCE4::compute_Ug1(body, r, t, tn, ...);</t>
+  </si>
+  <si>
+    <t>double Ug2 = SOURCE4::compute_Ug2(body, r, t, tn, ...);</t>
+  </si>
+  <si>
+    <t>double Ug3 = SOURCE4::compute_Ug3(body, r, t, tn, ...);</t>
+  </si>
+  <si>
+    <t>double Ug4 = SOURCE4::compute_Ug4(t, tn, ...);</t>
+  </si>
+  <si>
+    <t>// Feed into MUGE compressed Ug_sum term</t>
+  </si>
+  <si>
+    <t>SOURCE4::MUGEUgSumTerm ugsum_term;</t>
+  </si>
+  <si>
+    <t>params["Ug1"] = Ug1;</t>
+  </si>
+  <si>
+    <t>params["Ug2"] = Ug2;</t>
+  </si>
+  <si>
+    <t>params["Ug3"] = Ug3;</t>
+  </si>
+  <si>
+    <t>params["Ug4"] = Ug4;</t>
+  </si>
+  <si>
+    <t>double Ug_sum = ugsum_term.compute(t, params);</t>
+  </si>
+  <si>
+    <t>Scenario 2: MUGE Resonance → Compressed Feedback</t>
+  </si>
+  <si>
+    <t>// Resonance aDPM computed first</t>
+  </si>
+  <si>
+    <t>SOURCE4::MUGEResonanceADPMTerm adpm_term;</t>
+  </si>
+  <si>
+    <t>double aDPM = adpm_term.compute(t, params);</t>
+  </si>
+  <si>
+    <t>// Feed into all resonance sub-terms</t>
+  </si>
+  <si>
+    <t>params["aDPM"] = aDPM;</t>
+  </si>
+  <si>
+    <t>double aTHz = atHz_term.compute(t, params);</t>
+  </si>
+  <si>
+    <t>double aAetherRes = aether_res_term.compute(t, params);</t>
+  </si>
+  <si>
+    <t>// ... all 13 resonance terms depend on aDPM</t>
+  </si>
+  <si>
+    <t>Scenario 3: Fluid Solver → UQFF Forcing</t>
+  </si>
+  <si>
+    <t>// FluidSolver.step() with UQFF force injection</t>
+  </si>
+  <si>
+    <t>void FluidSolver::step(double dt, const std::map&lt;std::string, double&gt;&amp; uqff_params) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Compute MUGE g for current system</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    double g_force = SOURCE4::compute_compressed_MUGE(current_system);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Inject as body force in Navier-Stokes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    for (int i = 1; i &lt;= N; ++i) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        for (int j = 1; j &lt;= N; ++j) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            u[IX(i,j)] += dt * g_force * sin(j * PI / N);  // Jet profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Continue with NS solver steps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    diffuse(...);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    project(...);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    advect(...);</t>
+  </si>
+  <si>
+    <t>Scenario 4: Multi-System Batch Processing</t>
+  </si>
+  <si>
+    <t>// Compute all 7 systems simultaneously</t>
+  </si>
+  <si>
+    <t>std::vector&lt;SOURCE4::MUGESystem&gt; systems = {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    SOURCE4::sgr1745, SOURCE4::sagA, SOURCE4::tapestry,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    SOURCE4::westerlund, SOURCE4::pillars, SOURCE4::rings, SOURCE4::student_guide</t>
+  </si>
+  <si>
+    <t>for (const auto&amp; sys : systems) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    double g_c = SOURCE4::compute_compressed_MUGE(sys);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    double g_r = SOURCE4::compute_resonance_MUGE(sys, SOURCE4::res_params);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    std::cout &lt;&lt; sys.name &lt;&lt; " | Compressed: " &lt;&lt; g_c </t>
+  </si>
+  <si>
+    <t xml:space="preserve">              &lt;&lt; " | Resonance: " &lt;&lt; g_r &lt;&lt; std::endl;</t>
+  </si>
+  <si>
+    <t>FILE-BY-FILE INTEGRATION CHECKLIST</t>
+  </si>
+  <si>
+    <t>✅ source4.cpp (1782 lines)</t>
+  </si>
+  <si>
+    <t> Extract constants (lines 136-200) → namespace SOURCE4</t>
+  </si>
+  <si>
+    <t> Extract CelestialBody struct (177-191) → PART B</t>
+  </si>
+  <si>
+    <t> Extract MUGESystem struct (954-976) → PART B</t>
+  </si>
+  <si>
+    <t> Extract ResonanceParams struct (928-952) → PART B</t>
+  </si>
+  <si>
+    <t> Extract 6 helper functions (202-239) → PART H</t>
+  </si>
+  <si>
+    <t> Extract 8 UQFF functions (240-299) → PART H</t>
+  </si>
+  <si>
+    <t> Extract 10 MUGE compressed functions (1024-1095) → PART H</t>
+  </si>
+  <si>
+    <t> Extract 14 MUGE resonance functions (1097-1183) → PART H</t>
+  </si>
+  <si>
+    <t> Extract FluidSolver class (322-923) → PART I</t>
+  </si>
+  <si>
+    <t> Extract 7 system definitions (979-1021) → PART J</t>
+  </si>
+  <si>
+    <t> SKIP main() (lines 1616-1779) - test harness only</t>
+  </si>
+  <si>
+    <t> SKIP unit tests (1185-1614) - test harness only</t>
+  </si>
+  <si>
+    <t>✅ source4_wolfram.cpp (870 lines)</t>
+  </si>
+  <si>
+    <t> SKIP PhysicsTerm base (use MAIN_1_CoAnQi.cpp existing)</t>
+  </si>
+  <si>
+    <t> Extract UniversalGravity1-4 (15-141) → PART D</t>
+  </si>
+  <si>
+    <t> Extract UniversalBuoyancy (143-175) → PART D</t>
+  </si>
+  <si>
+    <t> Extract UniversalMagnetism (177-208) → PART D</t>
+  </si>
+  <si>
+    <t> Extract UniversalAether (210-232) → PART D</t>
+  </si>
+  <si>
+    <t> Extract UnifiedField (234-262) → PART D</t>
+  </si>
+  <si>
+    <t> Extract 6 helper terms (642-773) → PART C</t>
+  </si>
+  <si>
+    <t> Extract 7 system terms (447-637) → PART G</t>
+  </si>
+  <si>
+    <t> SKIP CompressedMUGETerm (265-337) - replaced by modular version</t>
+  </si>
+  <si>
+    <t> SKIP ResonanceMUGETerm (339-437) - replaced by modular version</t>
+  </si>
+  <si>
+    <t> SKIP NavierStokesQuasarJetTerm (808-826) - use FluidSolver instead</t>
+  </si>
+  <si>
+    <t> SKIP registration function (833-868) - inline registration</t>
+  </si>
+  <si>
+    <t>✅ source4_wolfram_compressed.cpp (312 lines)</t>
+  </si>
+  <si>
+    <t> SKIP PhysicsTerm base (use existing)</t>
+  </si>
+  <si>
+    <t> Extract 9 MUGE compressed classes (19-234) → PART E</t>
+  </si>
+  <si>
+    <t> SKIP registration function (241-251) - inline registration</t>
+  </si>
+  <si>
+    <t> SKIP example usage (254-312) - documentation only</t>
+  </si>
+  <si>
+    <t>✅ source4_wolfram_resonance.cpp (628 lines)</t>
+  </si>
+  <si>
+    <t> Extract 13 MUGE resonance classes (30-458) → PART F</t>
+  </si>
+  <si>
+    <t> SKIP registration function (464-512) - inline registration</t>
+  </si>
+  <si>
+    <t> SKIP example usage (517-627) - documentation only</t>
+  </si>
+  <si>
+    <t>POST-INTEGRATION VERIFICATION</t>
+  </si>
+  <si>
+    <t>Test Case 1: Individual Component Validation</t>
+  </si>
+  <si>
+    <r>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>CRITICAL:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> SKIP PhysicsTerm base (line 17) - REDEFINITION</t>
+    </r>
+  </si>
+  <si>
+    <t>// Verify each PhysicsTerm class computes non-zero values</t>
+  </si>
+  <si>
+    <t>SOURCE4::UniversalGravity1Term ug1;</t>
+  </si>
+  <si>
+    <t>assert(ug1.compute(0, params) != 0.0);</t>
+  </si>
+  <si>
+    <t>assert(ug1.getName() == "UniversalGravity1");</t>
+  </si>
+  <si>
+    <t>assert(ug1.validate(params) == true);</t>
+  </si>
+  <si>
+    <t>Test Case 2: UQFF Complete Calculation</t>
+  </si>
+  <si>
+    <t>CelestialBody earth = { /* parameters */ };</t>
+  </si>
+  <si>
+    <t>double FU = SOURCE4::compute_FU(earth, 1e7, 0, 0, 0);</t>
+  </si>
+  <si>
+    <t>// Expected: ~1e-3 to 1e-1 range (normalized)</t>
+  </si>
+  <si>
+    <t>assert(FU &gt; 1e-10 &amp;&amp; FU &lt; 1e3);</t>
+  </si>
+  <si>
+    <t>Test Case 3: MUGE Compressed vs Resonance</t>
+  </si>
+  <si>
+    <t>double g_c = SOURCE4::compute_compressed_MUGE(SOURCE4::sgr1745);</t>
+  </si>
+  <si>
+    <t>double g_r = SOURCE4::compute_resonance_MUGE(SOURCE4::sgr1745, SOURCE4::res_params);</t>
+  </si>
+  <si>
+    <t>// Both should be positive, resonance typically larger</t>
+  </si>
+  <si>
+    <t>assert(g_c &gt; 0 &amp;&amp; g_r &gt; 0);</t>
+  </si>
+  <si>
+    <t>std::cout &lt;&lt; "Ratio g_r/g_c: " &lt;&lt; g_r / g_c &lt;&lt; std::endl;</t>
+  </si>
+  <si>
+    <t>Test Case 4: Navier-Stokes Stability</t>
+  </si>
+  <si>
+    <t>SOURCE4::FluidSolver solver(64, 0.0001, 0.0);</t>
+  </si>
+  <si>
+    <t>solver.step(0.1, params);</t>
+  </si>
+  <si>
+    <t>// Check velocity field doesn't explode</t>
+  </si>
+  <si>
+    <t>assert(solver.getVelocityMagnitude(32, 32) &lt; 1e6);</t>
+  </si>
+  <si>
+    <t>SUMMARY: INTEGRATION EXECUTION PLAN</t>
+  </si>
+  <si>
+    <t>Total Work Estimate:</t>
+  </si>
+  <si>
+    <t>Integration Order:</t>
+  </si>
+  <si>
+    <t>1. Pre-flight: Verify PhysicsTerm exists in MAIN_1_CoAnQi.cpp ✅</t>
+  </si>
+  <si>
+    <t>Expected Build Impact:</t>
+  </si>
+  <si>
+    <t>Git Commit Message Template:</t>
+  </si>
+  <si>
+    <r>
+      <t>Lines to integrate:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 2,100 lines</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Classes to integrate:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 46 PhysicsTerm subclasses</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Functions to integrate:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 37 compute_* functions</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Data structures:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 3 structs</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Physics equations:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 30+ simultaneous equations</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2. Phase 1:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> Insert constants + data structures (103 lines)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>3. Phase 2:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> Insert helper classes (132 lines)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>4. Phase 3:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> Insert UQFF classes (244 lines)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>5. Phase 4:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> Insert MUGE compressed classes (216 lines)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>6. Phase 5:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> Insert MUGE resonance classes (429 lines)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>7. Phase 6:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> Insert astrophysical system classes (191 lines)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>8. Phase 7:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> Insert compute functions (257 lines)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>9. Phase 8:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> Insert FluidSolver (602 lines)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>10. Phase 9:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> Insert system instantiation (43 lines)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>11. Phase 10:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> Wrap entire block in </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>namespace SOURCE4 { }</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>12. Phase 11:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> Compile and resolve errors</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>13. Phase 12:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> Add menu option for validation</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>14. Phase 13:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> Test all 7 astrophysical systems</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>15. Phase 14:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> Git commit with detailed message</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Pre-integration:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 104,241 lines, 1.44 MB exe</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Post-integration:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 106,341 lines (+2,100), ~1.48 MB exe (+40 KB)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Compile time:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> +15-30 seconds (Visual Studio 2022)</t>
+    </r>
+  </si>
+  <si>
+    <t>SOURCE4 integration: UQFF + MUGE Compressed + MUGE Resonance + Navier-Stokes - Dec 5, 2025</t>
+  </si>
+  <si>
+    <t>Integrated 46 PhysicsTerm classes for simultaneous multi-physics solver:</t>
+  </si>
+  <si>
+    <t>- 8 Unified Field components (Ug1-4, Ubi, Um, A_μν, FU)</t>
+  </si>
+  <si>
+    <t>- 9 MUGE Compressed components (base, expansion, super, quantum, fluid, etc.)</t>
+  </si>
+  <si>
+    <t>- 13 MUGE Resonance components (aDPM, aTHz, wormhole, etc.)</t>
+  </si>
+  <si>
+    <t>- 7 Astrophysical systems (SGR1745, SagA*, Tapestry, etc.)</t>
+  </si>
+  <si>
+    <t>- 6 Helper functions (Ereact, mu_s, Bj, etc.)</t>
+  </si>
+  <si>
+    <t>- Jos Stam's Stable Fluids Navier-Stokes solver with UQFF coupling</t>
+  </si>
+  <si>
+    <t>Total: 2,100 lines, 37 compute_* functions, 3 data structures</t>
+  </si>
+  <si>
+    <t>Origin: source4.cpp (1782) + source4_wolfram*.cpp (1810)</t>
+  </si>
+  <si>
+    <t>This integration plan ensures:</t>
+  </si>
+  <si>
+    <t>✅ All physics equations preserved</t>
+  </si>
+  <si>
+    <t>✅ Simultaneous solver capability maintained</t>
+  </si>
+  <si>
+    <t>✅ No compilation conflicts</t>
+  </si>
+  <si>
+    <t>✅ Namespace isolation (SOURCE4)</t>
+  </si>
+  <si>
+    <t>✅ Compatible with existing MAIN_1_CoAnQi.cpp architecture</t>
+  </si>
+  <si>
+    <t>✅ 7 astrophysical systems ready for batch processing</t>
+  </si>
+  <si>
+    <t>✅ UQFF ↔ MUGE ↔ Navier-Stokes coupling enabled</t>
+  </si>
+  <si>
+    <t>Primary Recommendation: Create New File</t>
+  </si>
+  <si>
+    <t>Rationale:</t>
+  </si>
+  <si>
+    <t>Matches existing documentation pattern (e.g., BUILD_INSTRUCTIONS_PERMANENT.md, ENHANCEMENT_GUIDE.md)</t>
+  </si>
+  <si>
+    <t>Standalone file makes it easy to reference during integration work</t>
+  </si>
+  <si>
+    <t>Won't get lost in larger documents</t>
+  </si>
+  <si>
+    <t>Can be tracked in git as a planning artifact</t>
+  </si>
+  <si>
+    <t>Secondary Recommendation: Update Existing File</t>
+  </si>
+  <si>
+    <t>copilot-instructions.md (append to existing)</t>
+  </si>
+  <si>
+    <t>Already contains SOURCE82 integration history and patterns</t>
+  </si>
+  <si>
+    <t>This is where you document major integration events</t>
+  </si>
+  <si>
+    <t>Line 95 already references SOURCE115/116 integration with git commits</t>
+  </si>
+  <si>
+    <t>Natural place to add SOURCE4 integration plan for future reference</t>
+  </si>
+  <si>
+    <t>Suggested Action:</t>
+  </si>
+  <si>
+    <t>Option 1 (Recommended): Create both</t>
+  </si>
+  <si>
+    <t>2. copilot-instructions.md - Add summary entry:</t>
+  </si>
+  <si>
+    <r>
+      <t>Based on your project structure and documentation patterns, I recommend </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>two files</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> to preserve this integration plan:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SOURCE4_INTEGRATION_PLAN.md</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> (new file in workspace root)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1. SOURCE4_INTEGRATION_PLAN.md</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> - Full technical plan (as detailed above)</t>
+    </r>
+  </si>
+  <si>
+    <t>### Source4 Integration Status</t>
+  </si>
+  <si>
+    <t>- **Files:** source4.cpp (1782 lines) + source4_wolfram*.cpp (1810 lines)</t>
+  </si>
+  <si>
+    <t>- **Physics:** UQFF (8 components) + MUGE Compressed (9) + MUGE Resonance (13) + Navier-Stokes</t>
+  </si>
+  <si>
+    <t>- **Classes:** 46 PhysicsTerm subclasses + 37 compute_* functions</t>
+  </si>
+  <si>
+    <t>- **Plan:** SOURCE4_INTEGRATION_PLAN.md (comprehensive 5-phase integration strategy)</t>
+  </si>
+  <si>
+    <t>- **Status:** READY FOR INTEGRATION (Dec 5, 2025)</t>
+  </si>
+  <si>
+    <t>- **Target:** Insert as SOURCE4 block after SOURCE116, before SOURCE82</t>
+  </si>
+  <si>
+    <t>- **Impact:** +2,100 lines, +40KB exe size</t>
+  </si>
+  <si>
+    <t>Option 2 (Alternative): Single file</t>
+  </si>
+  <si>
+    <t>Update INTEGRATION_TRACKER.csv with new row:</t>
+  </si>
+  <si>
+    <t>source4.cpp,READY,46,UQFF+MUGE unified field solver (see SOURCE4_INTEGRATION_PLAN.md)</t>
+  </si>
+  <si>
+    <t>Option 3 (Quick): Copilot instructions only</t>
+  </si>
+  <si>
+    <t>Just update copilot-instructions.md with condensed version</t>
+  </si>
+  <si>
+    <t>Risk: Plan details may be lost if not captured in full</t>
+  </si>
+  <si>
+    <t>My recommendation: Create SOURCE4_INTEGRATION_PLAN.md now, then update copilot-instructions.md with reference after successful integration. This preserves both the detailed plan (for execution) and the historical record (for future context).</t>
+  </si>
+  <si>
+    <r>
+      <t>Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>SOURCE4_INTEGRATION_PLAN.md</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> with full details</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Would you like me to create </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>SOURCE4_INTEGRATION_PLAN.md</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> with the full integration plan?</t>
+    </r>
+  </si>
+  <si>
+    <t>Created SOURCE4_INTEGRATION_PLAN.md with the complete integration plan and conversation context.</t>
+  </si>
+  <si>
+    <t>The plan includes:</t>
+  </si>
+  <si>
+    <t>File-by-file checklists for source4.cpp and all wolfram files</t>
+  </si>
+  <si>
+    <t>Ready for integration execution when you're ready to proceed.</t>
+  </si>
+  <si>
+    <r>
+      <t>30+ physics equations</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> from UQFF, MUGE Compressed, MUGE Resonance, and Navier-Stokes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>46 PhysicsTerm classes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> organized in 5 parts (helpers, UQFF, compressed, resonance, systems)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>37 compute_ functions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>* for simultaneous solver</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>5-phase integration approach</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> with detailed extraction points</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Conflict resolution strategies</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> (PhysicsTerm redefinition, namespace isolation)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Validation test cases</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> and build impact estimates</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Conversation context</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> from today's analysis session</t>
     </r>
   </si>
 </sst>
@@ -11839,7 +14520,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="168">
+  <cellXfs count="185">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
@@ -12273,6 +14954,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -12286,6 +14970,38 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -12298,6 +15014,134 @@
 
 <file path=xl/activeX/activeX1.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D124-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX10.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX11.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX12.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX13.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX14.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX15.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX16.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX17.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX18.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX19.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX2.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX20.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX21.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX22.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX23.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX24.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX25.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX26.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX27.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX28.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX29.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX3.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX30.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX31.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX32.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX33.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX4.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX5.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX6.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX7.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX8.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX9.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -22585,7 +25429,7 @@
       <c r="D50" s="19"/>
     </row>
     <row r="51" spans="4:4" ht="17.25">
-      <c r="D51" s="163" t="s">
+      <c r="D51" s="164" t="s">
         <v>1530</v>
       </c>
     </row>
@@ -22669,7 +25513,7 @@
       </c>
     </row>
     <row r="69" spans="4:4">
-      <c r="D69" s="164" t="s">
+      <c r="D69" s="165" t="s">
         <v>1533</v>
       </c>
     </row>
@@ -22780,7 +25624,7 @@
       </c>
     </row>
     <row r="94" spans="4:4">
-      <c r="D94" s="165" t="s">
+      <c r="D94" s="166" t="s">
         <v>1564</v>
       </c>
     </row>
@@ -23433,7 +26277,7 @@
       </c>
     </row>
     <row r="245" spans="4:4" ht="17.25">
-      <c r="D245" s="166" t="s">
+      <c r="D245" s="167" t="s">
         <v>1657</v>
       </c>
     </row>
@@ -23591,7 +26435,7 @@
       </c>
     </row>
     <row r="279" spans="4:4" ht="17.25">
-      <c r="D279" s="166" t="s">
+      <c r="D279" s="167" t="s">
         <v>1671</v>
       </c>
     </row>
@@ -23636,7 +26480,7 @@
       </c>
     </row>
     <row r="288" spans="4:4" ht="17.25">
-      <c r="D288" s="166" t="s">
+      <c r="D288" s="167" t="s">
         <v>1676</v>
       </c>
     </row>
@@ -23677,7 +26521,7 @@
       </c>
     </row>
     <row r="298" spans="4:4" ht="17.25">
-      <c r="D298" s="166" t="s">
+      <c r="D298" s="167" t="s">
         <v>1697</v>
       </c>
     </row>
@@ -23959,12 +26803,12 @@
       </c>
     </row>
     <row r="361" spans="4:4" ht="28.5">
-      <c r="D361" s="167" t="s">
+      <c r="D361" s="168" t="s">
         <v>1745</v>
       </c>
     </row>
     <row r="363" spans="4:4" ht="17.25">
-      <c r="D363" s="166" t="s">
+      <c r="D363" s="167" t="s">
         <v>1746</v>
       </c>
     </row>
@@ -24576,10 +27420,451 @@
     <hyperlink ref="D436" r:id="rId48" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId49"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="D5:D91"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="4" max="4" width="97.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="5" spans="4:4" ht="17.25">
+      <c r="D5" s="164" t="s">
+        <v>1868</v>
+      </c>
+    </row>
+    <row r="6" spans="4:4">
+      <c r="D6" s="75" t="s">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="7" spans="4:4">
+      <c r="D7" s="80"/>
+    </row>
+    <row r="8" spans="4:4">
+      <c r="D8" s="81" t="s">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="9" spans="4:4">
+      <c r="D9" s="81" t="s">
+        <v>1871</v>
+      </c>
+    </row>
+    <row r="10" spans="4:4">
+      <c r="D10" s="82"/>
+    </row>
+    <row r="11" spans="4:4">
+      <c r="D11" s="83" t="s">
+        <v>1872</v>
+      </c>
+    </row>
+    <row r="12" spans="4:4">
+      <c r="D12" s="83" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="13" spans="4:4">
+      <c r="D13" s="83" t="s">
+        <v>1874</v>
+      </c>
+    </row>
+    <row r="14" spans="4:4">
+      <c r="D14" s="81" t="s">
+        <v>1875</v>
+      </c>
+    </row>
+    <row r="15" spans="4:4">
+      <c r="D15" s="82"/>
+    </row>
+    <row r="16" spans="4:4">
+      <c r="D16" s="83" t="s">
+        <v>1876</v>
+      </c>
+    </row>
+    <row r="17" spans="4:4">
+      <c r="D17" s="83" t="s">
+        <v>1877</v>
+      </c>
+    </row>
+    <row r="18" spans="4:4">
+      <c r="D18" s="83" t="s">
+        <v>1878</v>
+      </c>
+    </row>
+    <row r="19" spans="4:4">
+      <c r="D19" s="83" t="s">
+        <v>1879</v>
+      </c>
+    </row>
+    <row r="20" spans="4:4">
+      <c r="D20" s="81" t="s">
+        <v>1880</v>
+      </c>
+    </row>
+    <row r="21" spans="4:4">
+      <c r="D21" s="82"/>
+    </row>
+    <row r="22" spans="4:4">
+      <c r="D22" s="83" t="s">
+        <v>1881</v>
+      </c>
+    </row>
+    <row r="23" spans="4:4">
+      <c r="D23" s="83" t="s">
+        <v>1882</v>
+      </c>
+    </row>
+    <row r="24" spans="4:4">
+      <c r="D24" s="83" t="s">
+        <v>1883</v>
+      </c>
+    </row>
+    <row r="25" spans="4:4">
+      <c r="D25" s="83" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="26" spans="4:4">
+      <c r="D26" s="81" t="s">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="27" spans="4:4">
+      <c r="D27" s="82"/>
+    </row>
+    <row r="28" spans="4:4">
+      <c r="D28" s="83" t="s">
+        <v>1886</v>
+      </c>
+    </row>
+    <row r="29" spans="4:4">
+      <c r="D29" s="83" t="s">
+        <v>1887</v>
+      </c>
+    </row>
+    <row r="30" spans="4:4">
+      <c r="D30" s="83" t="s">
+        <v>1888</v>
+      </c>
+    </row>
+    <row r="31" spans="4:4">
+      <c r="D31" s="83" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="32" spans="4:4">
+      <c r="D32" s="83" t="s">
+        <v>1890</v>
+      </c>
+    </row>
+    <row r="33" spans="4:4">
+      <c r="D33" s="92" t="s">
+        <v>1891</v>
+      </c>
+    </row>
+    <row r="34" spans="4:4">
+      <c r="D34" s="82"/>
+    </row>
+    <row r="35" spans="4:4" ht="30">
+      <c r="D35" s="91" t="s">
+        <v>1892</v>
+      </c>
+    </row>
+    <row r="36" spans="4:4">
+      <c r="D36" s="83" t="s">
+        <v>1893</v>
+      </c>
+    </row>
+    <row r="37" spans="4:4">
+      <c r="D37" s="83" t="s">
+        <v>1894</v>
+      </c>
+    </row>
+    <row r="38" spans="4:4">
+      <c r="D38" s="19"/>
+    </row>
+    <row r="39" spans="4:4">
+      <c r="D39" s="75" t="s">
+        <v>1895</v>
+      </c>
+    </row>
+    <row r="40" spans="4:4" ht="17.25">
+      <c r="D40" s="164" t="s">
+        <v>1832</v>
+      </c>
+    </row>
+    <row r="41" spans="4:4">
+      <c r="D41" s="75" t="s">
+        <v>1833</v>
+      </c>
+    </row>
+    <row r="42" spans="4:4">
+      <c r="D42" s="80"/>
+    </row>
+    <row r="43" spans="4:4">
+      <c r="D43" s="82" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="44" spans="4:4">
+      <c r="D44" s="82"/>
+    </row>
+    <row r="45" spans="4:4">
+      <c r="D45" s="91" t="s">
+        <v>1834</v>
+      </c>
+    </row>
+    <row r="46" spans="4:4">
+      <c r="D46" s="91" t="s">
+        <v>1835</v>
+      </c>
+    </row>
+    <row r="47" spans="4:4">
+      <c r="D47" s="91" t="s">
+        <v>1836</v>
+      </c>
+    </row>
+    <row r="48" spans="4:4">
+      <c r="D48" s="91" t="s">
+        <v>1837</v>
+      </c>
+    </row>
+    <row r="49" spans="4:4">
+      <c r="D49" s="91" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="50" spans="4:4">
+      <c r="D50" s="91" t="s">
+        <v>1838</v>
+      </c>
+    </row>
+    <row r="51" spans="4:4">
+      <c r="D51" s="91" t="s">
+        <v>1839</v>
+      </c>
+    </row>
+    <row r="52" spans="4:4">
+      <c r="D52" s="91" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="53" spans="4:4">
+      <c r="D53" s="91" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="54" spans="4:4">
+      <c r="D54" s="91" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="55" spans="4:4">
+      <c r="D55" s="91" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="56" spans="4:4">
+      <c r="D56" s="91" t="s">
+        <v>1840</v>
+      </c>
+    </row>
+    <row r="57" spans="4:4">
+      <c r="D57" s="91" t="s">
+        <v>1841</v>
+      </c>
+    </row>
+    <row r="58" spans="4:4">
+      <c r="D58" s="91" t="s">
+        <v>1842</v>
+      </c>
+    </row>
+    <row r="59" spans="4:4">
+      <c r="D59" s="91" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="60" spans="4:4" ht="28.5">
+      <c r="D60" s="82" t="s">
+        <v>1848</v>
+      </c>
+    </row>
+    <row r="61" spans="4:4">
+      <c r="D61" s="82"/>
+    </row>
+    <row r="62" spans="4:4">
+      <c r="D62" s="83" t="s">
+        <v>1843</v>
+      </c>
+    </row>
+    <row r="63" spans="4:4">
+      <c r="D63" s="82" t="s">
+        <v>1849</v>
+      </c>
+    </row>
+    <row r="64" spans="4:4">
+      <c r="D64" s="82"/>
+    </row>
+    <row r="65" spans="4:4">
+      <c r="D65" s="83" t="s">
+        <v>1844</v>
+      </c>
+    </row>
+    <row r="66" spans="4:4">
+      <c r="D66" s="83" t="s">
+        <v>1845</v>
+      </c>
+    </row>
+    <row r="67" spans="4:4">
+      <c r="D67" s="19"/>
+    </row>
+    <row r="68" spans="4:4">
+      <c r="D68" s="75" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="69" spans="4:4">
+      <c r="D69" s="18" t="s">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="70" spans="4:4">
+      <c r="D70" s="18" t="s">
+        <v>1851</v>
+      </c>
+    </row>
+    <row r="71" spans="4:4">
+      <c r="D71" s="18" t="s">
+        <v>1852</v>
+      </c>
+    </row>
+    <row r="72" spans="4:4">
+      <c r="D72" s="18" t="s">
+        <v>1853</v>
+      </c>
+    </row>
+    <row r="73" spans="4:4">
+      <c r="D73" s="18" t="s">
+        <v>1854</v>
+      </c>
+    </row>
+    <row r="74" spans="4:4">
+      <c r="D74" s="18" t="s">
+        <v>1855</v>
+      </c>
+    </row>
+    <row r="75" spans="4:4">
+      <c r="D75" s="18"/>
+    </row>
+    <row r="76" spans="4:4">
+      <c r="D76" s="75" t="s">
+        <v>1856</v>
+      </c>
+    </row>
+    <row r="77" spans="4:4">
+      <c r="D77" s="80"/>
+    </row>
+    <row r="78" spans="4:4">
+      <c r="D78" s="82" t="s">
+        <v>1866</v>
+      </c>
+    </row>
+    <row r="79" spans="4:4">
+      <c r="D79" s="82" t="s">
+        <v>1867</v>
+      </c>
+    </row>
+    <row r="80" spans="4:4">
+      <c r="D80" s="82" t="s">
+        <v>1857</v>
+      </c>
+    </row>
+    <row r="81" spans="4:4">
+      <c r="D81" s="19"/>
+    </row>
+    <row r="82" spans="4:4">
+      <c r="D82" s="75" t="s">
+        <v>1858</v>
+      </c>
+    </row>
+    <row r="83" spans="4:4">
+      <c r="D83" s="80"/>
+    </row>
+    <row r="84" spans="4:4">
+      <c r="D84" s="81" t="s">
+        <v>1859</v>
+      </c>
+    </row>
+    <row r="85" spans="4:4">
+      <c r="D85" s="81" t="s">
+        <v>1860</v>
+      </c>
+    </row>
+    <row r="86" spans="4:4">
+      <c r="D86" s="81" t="s">
+        <v>1861</v>
+      </c>
+    </row>
+    <row r="87" spans="4:4">
+      <c r="D87" s="82" t="s">
+        <v>1862</v>
+      </c>
+    </row>
+    <row r="88" spans="4:4">
+      <c r="D88" s="82" t="s">
+        <v>1863</v>
+      </c>
+    </row>
+    <row r="89" spans="4:4">
+      <c r="D89" s="82" t="s">
+        <v>1864</v>
+      </c>
+    </row>
+    <row r="90" spans="4:4">
+      <c r="D90" s="19"/>
+    </row>
+    <row r="91" spans="4:4">
+      <c r="D91" s="89" t="s">
+        <v>1865</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D45" r:id="rId1" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D46" r:id="rId2" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D47" r:id="rId3" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D48" r:id="rId4" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D49" r:id="rId5" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D50" r:id="rId6" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D51" r:id="rId7" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D52" r:id="rId8" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D53" r:id="rId9" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D54" r:id="rId10" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D55" r:id="rId11" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D56" r:id="rId12" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D57" r:id="rId13" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D58" r:id="rId14" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D59" r:id="rId15" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D84" r:id="rId16" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D85" r:id="rId17" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D86" r:id="rId18" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D8" r:id="rId19" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D9" r:id="rId20" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D14" r:id="rId21" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D20" r:id="rId22" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D26" r:id="rId23" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D35" r:id="rId24" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="E5:E235"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
@@ -25547,4 +28832,3591 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId37"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr codeName="Hoja2"/>
+  <dimension ref="D5:M638"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="4" max="4" width="123.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.85546875" customWidth="1"/>
+    <col min="6" max="6" width="60.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="73.28515625" customWidth="1"/>
+    <col min="8" max="8" width="14.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="5" spans="4:4">
+      <c r="D5" s="16" t="s">
+        <v>1896</v>
+      </c>
+    </row>
+    <row r="6" spans="4:4" ht="17.25">
+      <c r="D6" s="157" t="s">
+        <v>1897</v>
+      </c>
+    </row>
+    <row r="7" spans="4:4" ht="28.5">
+      <c r="D7" s="7" t="s">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="8" spans="4:4">
+      <c r="D8" s="7" t="s">
+        <v>1901</v>
+      </c>
+    </row>
+    <row r="9" spans="4:4">
+      <c r="D9" s="7" t="s">
+        <v>1902</v>
+      </c>
+    </row>
+    <row r="10" spans="4:4">
+      <c r="D10" s="7" t="s">
+        <v>1903</v>
+      </c>
+    </row>
+    <row r="11" spans="4:4">
+      <c r="D11" s="5"/>
+    </row>
+    <row r="12" spans="4:4">
+      <c r="D12" s="5"/>
+    </row>
+    <row r="13" spans="4:4" ht="17.25">
+      <c r="D13" s="157" t="s">
+        <v>1898</v>
+      </c>
+    </row>
+    <row r="14" spans="4:4">
+      <c r="D14" s="7" t="s">
+        <v>1899</v>
+      </c>
+    </row>
+    <row r="15" spans="4:4">
+      <c r="D15" t="s">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="17" spans="4:13">
+      <c r="D17" s="170" t="s">
+        <v>1905</v>
+      </c>
+      <c r="E17" s="170" t="s">
+        <v>1906</v>
+      </c>
+      <c r="F17" s="170" t="s">
+        <v>1907</v>
+      </c>
+      <c r="G17" s="170" t="s">
+        <v>1908</v>
+      </c>
+      <c r="H17" s="114"/>
+      <c r="I17" s="114"/>
+      <c r="J17" s="114"/>
+      <c r="K17" s="114"/>
+      <c r="L17" s="114"/>
+      <c r="M17" s="114"/>
+    </row>
+    <row r="18" spans="4:13">
+      <c r="D18" s="171" t="s">
+        <v>1909</v>
+      </c>
+      <c r="E18" s="172" t="s">
+        <v>1910</v>
+      </c>
+      <c r="F18" s="173" t="s">
+        <v>1911</v>
+      </c>
+      <c r="G18" s="172" t="s">
+        <v>1912</v>
+      </c>
+      <c r="H18" s="114"/>
+      <c r="I18" s="114"/>
+      <c r="J18" s="114"/>
+      <c r="K18" s="114"/>
+      <c r="L18" s="114"/>
+      <c r="M18" s="114"/>
+    </row>
+    <row r="19" spans="4:13">
+      <c r="D19" s="171" t="s">
+        <v>1913</v>
+      </c>
+      <c r="E19" s="172" t="s">
+        <v>1914</v>
+      </c>
+      <c r="F19" s="173" t="s">
+        <v>1915</v>
+      </c>
+      <c r="G19" s="172" t="s">
+        <v>1916</v>
+      </c>
+      <c r="H19" s="114"/>
+      <c r="I19" s="114"/>
+      <c r="J19" s="114"/>
+      <c r="K19" s="114"/>
+      <c r="L19" s="114"/>
+      <c r="M19" s="114"/>
+    </row>
+    <row r="20" spans="4:13">
+      <c r="D20" s="171" t="s">
+        <v>1917</v>
+      </c>
+      <c r="E20" s="172" t="s">
+        <v>1918</v>
+      </c>
+      <c r="F20" s="173" t="s">
+        <v>1919</v>
+      </c>
+      <c r="G20" s="172" t="s">
+        <v>1920</v>
+      </c>
+      <c r="H20" s="114"/>
+      <c r="I20" s="114"/>
+      <c r="J20" s="114"/>
+      <c r="K20" s="114"/>
+      <c r="L20" s="114"/>
+      <c r="M20" s="114"/>
+    </row>
+    <row r="21" spans="4:13">
+      <c r="D21" s="171" t="s">
+        <v>1921</v>
+      </c>
+      <c r="E21" s="172" t="s">
+        <v>1922</v>
+      </c>
+      <c r="F21" s="173" t="s">
+        <v>1923</v>
+      </c>
+      <c r="G21" s="172" t="s">
+        <v>1924</v>
+      </c>
+      <c r="H21" s="114"/>
+      <c r="I21" s="114"/>
+      <c r="J21" s="114"/>
+      <c r="K21" s="114"/>
+      <c r="L21" s="114"/>
+      <c r="M21" s="114"/>
+    </row>
+    <row r="22" spans="4:13">
+      <c r="D22" s="171" t="s">
+        <v>1925</v>
+      </c>
+      <c r="E22" s="172" t="s">
+        <v>1926</v>
+      </c>
+      <c r="F22" s="174" t="s">
+        <v>1927</v>
+      </c>
+      <c r="G22" s="172" t="s">
+        <v>1928</v>
+      </c>
+      <c r="H22" s="114"/>
+      <c r="I22" s="114"/>
+      <c r="J22" s="114"/>
+      <c r="K22" s="114"/>
+      <c r="L22" s="114"/>
+      <c r="M22" s="114"/>
+    </row>
+    <row r="23" spans="4:13">
+      <c r="D23" s="171" t="s">
+        <v>1929</v>
+      </c>
+      <c r="E23" s="172" t="s">
+        <v>1930</v>
+      </c>
+      <c r="F23" s="174" t="s">
+        <v>1931</v>
+      </c>
+      <c r="G23" s="172" t="s">
+        <v>1932</v>
+      </c>
+      <c r="H23" s="114"/>
+      <c r="I23" s="114"/>
+      <c r="J23" s="114"/>
+      <c r="K23" s="114"/>
+      <c r="L23" s="114"/>
+      <c r="M23" s="114"/>
+    </row>
+    <row r="24" spans="4:13">
+      <c r="D24" s="171" t="s">
+        <v>1933</v>
+      </c>
+      <c r="E24" s="172" t="s">
+        <v>1934</v>
+      </c>
+      <c r="F24" s="174" t="s">
+        <v>1935</v>
+      </c>
+      <c r="G24" s="172" t="s">
+        <v>1936</v>
+      </c>
+      <c r="H24" s="114"/>
+      <c r="I24" s="114"/>
+      <c r="J24" s="114"/>
+      <c r="K24" s="114"/>
+      <c r="L24" s="114"/>
+      <c r="M24" s="114"/>
+    </row>
+    <row r="25" spans="4:13">
+      <c r="D25" s="171" t="s">
+        <v>1937</v>
+      </c>
+      <c r="E25" s="172" t="s">
+        <v>1938</v>
+      </c>
+      <c r="F25" s="173" t="s">
+        <v>1939</v>
+      </c>
+      <c r="G25" s="172" t="s">
+        <v>1940</v>
+      </c>
+      <c r="H25" s="114"/>
+      <c r="I25" s="114"/>
+      <c r="J25" s="114"/>
+      <c r="K25" s="114"/>
+      <c r="L25" s="114"/>
+      <c r="M25" s="114"/>
+    </row>
+    <row r="26" spans="4:13">
+      <c r="D26" s="171" t="s">
+        <v>1941</v>
+      </c>
+      <c r="E26" s="175"/>
+      <c r="F26" s="175"/>
+      <c r="G26" s="175"/>
+      <c r="H26" s="114"/>
+      <c r="I26" s="114"/>
+      <c r="J26" s="114"/>
+      <c r="K26" s="114"/>
+      <c r="L26" s="114"/>
+      <c r="M26" s="114"/>
+    </row>
+    <row r="27" spans="4:13">
+      <c r="D27" s="176"/>
+      <c r="E27" s="175"/>
+      <c r="F27" s="175"/>
+      <c r="G27" s="175"/>
+      <c r="H27" s="114"/>
+      <c r="I27" s="114"/>
+      <c r="J27" s="114"/>
+      <c r="K27" s="114"/>
+      <c r="L27" s="114"/>
+      <c r="M27" s="114"/>
+    </row>
+    <row r="28" spans="4:13">
+      <c r="D28" s="177" t="s">
+        <v>1942</v>
+      </c>
+      <c r="E28" s="175"/>
+      <c r="F28" s="175"/>
+      <c r="G28" s="175"/>
+      <c r="H28" s="114"/>
+      <c r="I28" s="114"/>
+      <c r="J28" s="114"/>
+      <c r="K28" s="114"/>
+      <c r="L28" s="114"/>
+      <c r="M28" s="114"/>
+    </row>
+    <row r="29" spans="4:13">
+      <c r="D29" s="178" t="s">
+        <v>1943</v>
+      </c>
+      <c r="E29" s="175"/>
+      <c r="F29" s="175"/>
+      <c r="G29" s="175"/>
+      <c r="H29" s="114"/>
+      <c r="I29" s="114"/>
+      <c r="J29" s="114"/>
+      <c r="K29" s="114"/>
+      <c r="L29" s="114"/>
+      <c r="M29" s="114"/>
+    </row>
+    <row r="30" spans="4:13">
+      <c r="D30" s="177" t="s">
+        <v>1944</v>
+      </c>
+      <c r="E30" s="175"/>
+      <c r="F30" s="175"/>
+      <c r="G30" s="175"/>
+      <c r="H30" s="114"/>
+      <c r="I30" s="114"/>
+      <c r="J30" s="114"/>
+      <c r="K30" s="114"/>
+      <c r="L30" s="114"/>
+      <c r="M30" s="114"/>
+    </row>
+    <row r="31" spans="4:13">
+      <c r="D31" s="178" t="s">
+        <v>1945</v>
+      </c>
+      <c r="E31" s="175"/>
+      <c r="F31" s="175"/>
+      <c r="G31" s="175"/>
+      <c r="H31" s="114"/>
+      <c r="I31" s="114"/>
+      <c r="J31" s="114"/>
+      <c r="K31" s="114"/>
+      <c r="L31" s="114"/>
+      <c r="M31" s="114"/>
+    </row>
+    <row r="32" spans="4:13">
+      <c r="D32" s="177" t="s">
+        <v>1946</v>
+      </c>
+      <c r="E32" s="175"/>
+      <c r="F32" s="175"/>
+      <c r="G32" s="175"/>
+      <c r="H32" s="114"/>
+      <c r="I32" s="114"/>
+      <c r="J32" s="114"/>
+      <c r="K32" s="114"/>
+      <c r="L32" s="114"/>
+      <c r="M32" s="114"/>
+    </row>
+    <row r="33" spans="4:13">
+      <c r="D33" s="178" t="s">
+        <v>1947</v>
+      </c>
+      <c r="E33" s="175"/>
+      <c r="F33" s="175"/>
+      <c r="G33" s="175"/>
+      <c r="H33" s="114"/>
+      <c r="I33" s="114"/>
+      <c r="J33" s="114"/>
+      <c r="K33" s="114"/>
+      <c r="L33" s="114"/>
+      <c r="M33" s="114"/>
+    </row>
+    <row r="34" spans="4:13">
+      <c r="D34" s="175"/>
+      <c r="E34" s="175"/>
+      <c r="F34" s="175"/>
+      <c r="G34" s="175"/>
+      <c r="H34" s="114"/>
+      <c r="I34" s="114"/>
+      <c r="J34" s="114"/>
+      <c r="K34" s="114"/>
+      <c r="L34" s="114"/>
+      <c r="M34" s="114"/>
+    </row>
+    <row r="35" spans="4:13">
+      <c r="D35" s="175"/>
+      <c r="E35" s="175"/>
+      <c r="F35" s="175"/>
+      <c r="G35" s="175"/>
+      <c r="H35" s="114"/>
+      <c r="I35" s="114"/>
+      <c r="J35" s="114"/>
+      <c r="K35" s="114"/>
+      <c r="L35" s="114"/>
+      <c r="M35" s="114"/>
+    </row>
+    <row r="36" spans="4:13">
+      <c r="D36" s="175"/>
+      <c r="E36" s="175"/>
+      <c r="F36" s="175"/>
+      <c r="G36" s="175"/>
+      <c r="H36" s="114"/>
+      <c r="I36" s="114"/>
+      <c r="J36" s="114"/>
+      <c r="K36" s="114"/>
+      <c r="L36" s="114"/>
+      <c r="M36" s="114"/>
+    </row>
+    <row r="37" spans="4:13">
+      <c r="D37" s="171" t="s">
+        <v>1948</v>
+      </c>
+      <c r="E37" s="175"/>
+      <c r="F37" s="175"/>
+      <c r="G37" s="175"/>
+      <c r="H37" s="114"/>
+      <c r="I37" s="114"/>
+      <c r="J37" s="114"/>
+      <c r="K37" s="114"/>
+      <c r="L37" s="114"/>
+      <c r="M37" s="114"/>
+    </row>
+    <row r="38" spans="4:13">
+      <c r="D38" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="40" spans="4:13">
+      <c r="D40" s="170" t="s">
+        <v>1905</v>
+      </c>
+      <c r="E40" s="170" t="s">
+        <v>1906</v>
+      </c>
+      <c r="F40" s="170" t="s">
+        <v>1950</v>
+      </c>
+      <c r="G40" s="170" t="s">
+        <v>1908</v>
+      </c>
+    </row>
+    <row r="41" spans="4:13">
+      <c r="D41" s="171" t="s">
+        <v>1951</v>
+      </c>
+      <c r="E41" s="172" t="s">
+        <v>1952</v>
+      </c>
+      <c r="F41" s="173" t="s">
+        <v>1953</v>
+      </c>
+      <c r="G41" s="172" t="s">
+        <v>1954</v>
+      </c>
+    </row>
+    <row r="42" spans="4:13">
+      <c r="D42" s="171" t="s">
+        <v>1955</v>
+      </c>
+      <c r="E42" s="172" t="s">
+        <v>1956</v>
+      </c>
+      <c r="F42" s="173" t="s">
+        <v>1957</v>
+      </c>
+      <c r="G42" s="172" t="s">
+        <v>1958</v>
+      </c>
+    </row>
+    <row r="43" spans="4:13">
+      <c r="D43" s="171" t="s">
+        <v>1959</v>
+      </c>
+      <c r="E43" s="172" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F43" s="174" t="s">
+        <v>1961</v>
+      </c>
+      <c r="G43" s="172" t="s">
+        <v>1962</v>
+      </c>
+    </row>
+    <row r="44" spans="4:13">
+      <c r="D44" s="171" t="s">
+        <v>1963</v>
+      </c>
+      <c r="E44" s="172" t="s">
+        <v>1964</v>
+      </c>
+      <c r="F44" s="174">
+        <v>1</v>
+      </c>
+      <c r="G44" s="172" t="s">
+        <v>1965</v>
+      </c>
+    </row>
+    <row r="45" spans="4:13">
+      <c r="D45" s="171" t="s">
+        <v>1966</v>
+      </c>
+      <c r="E45" s="172" t="s">
+        <v>1967</v>
+      </c>
+      <c r="F45" s="173" t="s">
+        <v>1968</v>
+      </c>
+      <c r="G45" s="172" t="s">
+        <v>1969</v>
+      </c>
+    </row>
+    <row r="46" spans="4:13">
+      <c r="D46" s="171" t="s">
+        <v>1970</v>
+      </c>
+      <c r="E46" s="172" t="s">
+        <v>1971</v>
+      </c>
+      <c r="F46" s="173" t="s">
+        <v>1972</v>
+      </c>
+      <c r="G46" s="172" t="s">
+        <v>1973</v>
+      </c>
+    </row>
+    <row r="47" spans="4:13">
+      <c r="D47" s="171" t="s">
+        <v>1974</v>
+      </c>
+      <c r="E47" s="172" t="s">
+        <v>1975</v>
+      </c>
+      <c r="F47" s="174" t="s">
+        <v>1976</v>
+      </c>
+      <c r="G47" s="172" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="48" spans="4:13">
+      <c r="D48" s="171" t="s">
+        <v>1978</v>
+      </c>
+      <c r="E48" s="172" t="s">
+        <v>1979</v>
+      </c>
+      <c r="F48" s="173" t="s">
+        <v>1980</v>
+      </c>
+      <c r="G48" s="172" t="s">
+        <v>1981</v>
+      </c>
+    </row>
+    <row r="49" spans="4:7">
+      <c r="D49" s="171" t="s">
+        <v>1982</v>
+      </c>
+      <c r="E49" s="172" t="s">
+        <v>1983</v>
+      </c>
+      <c r="F49" s="173" t="s">
+        <v>1984</v>
+      </c>
+      <c r="G49" s="172" t="s">
+        <v>1985</v>
+      </c>
+    </row>
+    <row r="50" spans="4:7">
+      <c r="D50" s="173" t="s">
+        <v>1986</v>
+      </c>
+      <c r="E50" s="175"/>
+      <c r="F50" s="175"/>
+      <c r="G50" s="175"/>
+    </row>
+    <row r="51" spans="4:7">
+      <c r="D51" s="175"/>
+      <c r="E51" s="175"/>
+      <c r="F51" s="175"/>
+      <c r="G51" s="175"/>
+    </row>
+    <row r="52" spans="4:7">
+      <c r="D52" s="175"/>
+      <c r="E52" s="175"/>
+      <c r="F52" s="175"/>
+      <c r="G52" s="175"/>
+    </row>
+    <row r="53" spans="4:7">
+      <c r="D53" s="171" t="s">
+        <v>1987</v>
+      </c>
+      <c r="E53" s="175"/>
+      <c r="F53" s="175"/>
+      <c r="G53" s="175"/>
+    </row>
+    <row r="54" spans="4:7">
+      <c r="D54" t="s">
+        <v>1988</v>
+      </c>
+    </row>
+    <row r="55" spans="4:7">
+      <c r="D55" t="s">
+        <v>1989</v>
+      </c>
+    </row>
+    <row r="56" spans="4:7">
+      <c r="D56" t="s">
+        <v>1990</v>
+      </c>
+    </row>
+    <row r="58" spans="4:7">
+      <c r="D58" s="170" t="s">
+        <v>1905</v>
+      </c>
+      <c r="E58" s="170" t="s">
+        <v>1906</v>
+      </c>
+      <c r="F58" s="170" t="s">
+        <v>1950</v>
+      </c>
+      <c r="G58" s="170" t="s">
+        <v>1908</v>
+      </c>
+    </row>
+    <row r="59" spans="4:7">
+      <c r="D59" s="171" t="s">
+        <v>1991</v>
+      </c>
+      <c r="E59" s="172" t="s">
+        <v>1992</v>
+      </c>
+      <c r="F59" s="174" t="s">
+        <v>1993</v>
+      </c>
+      <c r="G59" s="172" t="s">
+        <v>1994</v>
+      </c>
+    </row>
+    <row r="60" spans="4:7">
+      <c r="D60" s="171" t="s">
+        <v>1995</v>
+      </c>
+      <c r="E60" s="172" t="s">
+        <v>1996</v>
+      </c>
+      <c r="F60" s="173" t="s">
+        <v>1997</v>
+      </c>
+      <c r="G60" s="172" t="s">
+        <v>1998</v>
+      </c>
+    </row>
+    <row r="61" spans="4:7">
+      <c r="D61" s="171" t="s">
+        <v>1999</v>
+      </c>
+      <c r="E61" s="172" t="s">
+        <v>2000</v>
+      </c>
+      <c r="F61" s="173" t="s">
+        <v>2001</v>
+      </c>
+      <c r="G61" s="172" t="s">
+        <v>2002</v>
+      </c>
+    </row>
+    <row r="62" spans="4:7">
+      <c r="D62" s="171" t="s">
+        <v>2003</v>
+      </c>
+      <c r="E62" s="172" t="s">
+        <v>2004</v>
+      </c>
+      <c r="F62" s="173" t="s">
+        <v>2005</v>
+      </c>
+      <c r="G62" s="172" t="s">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="63" spans="4:7">
+      <c r="D63" s="171" t="s">
+        <v>2007</v>
+      </c>
+      <c r="E63" s="172" t="s">
+        <v>2008</v>
+      </c>
+      <c r="F63" s="173" t="s">
+        <v>2009</v>
+      </c>
+      <c r="G63" s="172" t="s">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="64" spans="4:7">
+      <c r="D64" s="171" t="s">
+        <v>2011</v>
+      </c>
+      <c r="E64" s="172" t="s">
+        <v>2012</v>
+      </c>
+      <c r="F64" s="173" t="s">
+        <v>2013</v>
+      </c>
+      <c r="G64" s="172" t="s">
+        <v>2014</v>
+      </c>
+    </row>
+    <row r="65" spans="4:7">
+      <c r="D65" s="171" t="s">
+        <v>2015</v>
+      </c>
+      <c r="E65" s="172" t="s">
+        <v>2016</v>
+      </c>
+      <c r="F65" s="173" t="s">
+        <v>2017</v>
+      </c>
+      <c r="G65" s="172" t="s">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="66" spans="4:7">
+      <c r="D66" s="171" t="s">
+        <v>2019</v>
+      </c>
+      <c r="E66" s="172" t="s">
+        <v>2020</v>
+      </c>
+      <c r="F66" s="173" t="s">
+        <v>2021</v>
+      </c>
+      <c r="G66" s="172" t="s">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="67" spans="4:7">
+      <c r="D67" s="171" t="s">
+        <v>2023</v>
+      </c>
+      <c r="E67" s="172" t="s">
+        <v>2024</v>
+      </c>
+      <c r="F67" s="173" t="s">
+        <v>2025</v>
+      </c>
+      <c r="G67" s="172" t="s">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="68" spans="4:7">
+      <c r="D68" s="171" t="s">
+        <v>2027</v>
+      </c>
+      <c r="E68" s="172" t="s">
+        <v>2028</v>
+      </c>
+      <c r="F68" s="173" t="s">
+        <v>2029</v>
+      </c>
+      <c r="G68" s="172" t="s">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="69" spans="4:7">
+      <c r="D69" s="171" t="s">
+        <v>2031</v>
+      </c>
+      <c r="E69" s="172" t="s">
+        <v>2032</v>
+      </c>
+      <c r="F69" s="173" t="s">
+        <v>2033</v>
+      </c>
+      <c r="G69" s="172" t="s">
+        <v>2034</v>
+      </c>
+    </row>
+    <row r="70" spans="4:7">
+      <c r="D70" s="171" t="s">
+        <v>2035</v>
+      </c>
+      <c r="E70" s="172" t="s">
+        <v>2036</v>
+      </c>
+      <c r="F70" s="174" t="s">
+        <v>2037</v>
+      </c>
+      <c r="G70" s="172" t="s">
+        <v>2038</v>
+      </c>
+    </row>
+    <row r="71" spans="4:7">
+      <c r="D71" s="171" t="s">
+        <v>2039</v>
+      </c>
+      <c r="E71" s="172" t="s">
+        <v>2040</v>
+      </c>
+      <c r="F71" s="173" t="s">
+        <v>2041</v>
+      </c>
+      <c r="G71" s="172" t="s">
+        <v>2042</v>
+      </c>
+    </row>
+    <row r="72" spans="4:7">
+      <c r="D72" s="173" t="s">
+        <v>2043</v>
+      </c>
+      <c r="E72" s="175"/>
+      <c r="F72" s="175"/>
+      <c r="G72" s="175"/>
+    </row>
+    <row r="73" spans="4:7">
+      <c r="D73" s="175"/>
+      <c r="E73" s="175"/>
+      <c r="F73" s="175"/>
+      <c r="G73" s="175"/>
+    </row>
+    <row r="74" spans="4:7">
+      <c r="D74" s="175"/>
+      <c r="E74" s="175"/>
+      <c r="F74" s="175"/>
+      <c r="G74" s="175"/>
+    </row>
+    <row r="75" spans="4:7">
+      <c r="D75" s="171" t="s">
+        <v>2044</v>
+      </c>
+      <c r="E75" s="175"/>
+      <c r="F75" s="175"/>
+      <c r="G75" s="175"/>
+    </row>
+    <row r="76" spans="4:7">
+      <c r="D76" t="s">
+        <v>2045</v>
+      </c>
+    </row>
+    <row r="77" spans="4:7">
+      <c r="D77" t="s">
+        <v>2046</v>
+      </c>
+    </row>
+    <row r="78" spans="4:7">
+      <c r="D78" s="179" t="s">
+        <v>2048</v>
+      </c>
+    </row>
+    <row r="79" spans="4:7">
+      <c r="D79" t="s">
+        <v>2047</v>
+      </c>
+    </row>
+    <row r="81" spans="4:8">
+      <c r="D81" s="171" t="s">
+        <v>2049</v>
+      </c>
+      <c r="E81" s="175"/>
+      <c r="F81" s="175"/>
+      <c r="G81" s="175"/>
+      <c r="H81" s="175"/>
+    </row>
+    <row r="82" spans="4:8">
+      <c r="D82" s="176"/>
+      <c r="E82" s="175"/>
+      <c r="F82" s="175"/>
+      <c r="G82" s="175"/>
+      <c r="H82" s="175"/>
+    </row>
+    <row r="83" spans="4:8">
+      <c r="D83" s="180" t="s">
+        <v>2113</v>
+      </c>
+      <c r="E83" s="175"/>
+      <c r="F83" s="175"/>
+      <c r="G83" s="175"/>
+      <c r="H83" s="175"/>
+    </row>
+    <row r="84" spans="4:8">
+      <c r="D84" s="178" t="s">
+        <v>2050</v>
+      </c>
+      <c r="E84" s="175"/>
+      <c r="F84" s="175"/>
+      <c r="G84" s="175"/>
+      <c r="H84" s="175"/>
+    </row>
+    <row r="85" spans="4:8">
+      <c r="D85" s="178" t="s">
+        <v>2051</v>
+      </c>
+      <c r="E85" s="175"/>
+      <c r="F85" s="175"/>
+      <c r="G85" s="175"/>
+      <c r="H85" s="175"/>
+    </row>
+    <row r="86" spans="4:8">
+      <c r="D86" s="178" t="s">
+        <v>2052</v>
+      </c>
+      <c r="E86" s="175"/>
+      <c r="F86" s="175"/>
+      <c r="G86" s="175"/>
+      <c r="H86" s="175"/>
+    </row>
+    <row r="87" spans="4:8">
+      <c r="D87" s="178" t="s">
+        <v>2053</v>
+      </c>
+      <c r="E87" s="175"/>
+      <c r="F87" s="175"/>
+      <c r="G87" s="175"/>
+      <c r="H87" s="175"/>
+    </row>
+    <row r="88" spans="4:8">
+      <c r="D88" s="178" t="s">
+        <v>2054</v>
+      </c>
+      <c r="E88" s="175"/>
+      <c r="F88" s="175"/>
+      <c r="G88" s="175"/>
+      <c r="H88" s="175"/>
+    </row>
+    <row r="89" spans="4:8">
+      <c r="D89" s="175"/>
+      <c r="E89" s="175"/>
+      <c r="F89" s="175"/>
+      <c r="G89" s="175"/>
+      <c r="H89" s="175"/>
+    </row>
+    <row r="90" spans="4:8">
+      <c r="D90" s="175"/>
+      <c r="E90" s="175"/>
+      <c r="F90" s="175"/>
+      <c r="G90" s="175"/>
+      <c r="H90" s="175"/>
+    </row>
+    <row r="91" spans="4:8">
+      <c r="D91" s="175"/>
+      <c r="E91" s="175"/>
+      <c r="F91" s="175"/>
+      <c r="G91" s="175"/>
+      <c r="H91" s="175"/>
+    </row>
+    <row r="92" spans="4:8">
+      <c r="D92" s="171" t="s">
+        <v>2055</v>
+      </c>
+      <c r="E92" s="175"/>
+      <c r="F92" s="175"/>
+      <c r="G92" s="175"/>
+      <c r="H92" s="175"/>
+    </row>
+    <row r="93" spans="4:8">
+      <c r="D93" s="170" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E93" s="170" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F93" s="170" t="s">
+        <v>2058</v>
+      </c>
+      <c r="G93" s="175"/>
+      <c r="H93" s="175"/>
+    </row>
+    <row r="94" spans="4:8">
+      <c r="D94" s="171" t="s">
+        <v>2059</v>
+      </c>
+      <c r="E94" s="172" t="s">
+        <v>2060</v>
+      </c>
+      <c r="F94" s="172" t="s">
+        <v>2061</v>
+      </c>
+      <c r="G94" s="175"/>
+      <c r="H94" s="175"/>
+    </row>
+    <row r="95" spans="4:8">
+      <c r="D95" s="171" t="s">
+        <v>2114</v>
+      </c>
+      <c r="E95" s="172" t="s">
+        <v>2062</v>
+      </c>
+      <c r="F95" s="172" t="s">
+        <v>2063</v>
+      </c>
+      <c r="G95" s="175"/>
+      <c r="H95" s="175"/>
+    </row>
+    <row r="96" spans="4:8">
+      <c r="D96" s="171" t="s">
+        <v>2064</v>
+      </c>
+      <c r="E96" s="172" t="s">
+        <v>2065</v>
+      </c>
+      <c r="F96" s="172" t="s">
+        <v>2066</v>
+      </c>
+      <c r="G96" s="175"/>
+      <c r="H96" s="175"/>
+    </row>
+    <row r="97" spans="4:8">
+      <c r="D97" s="171" t="s">
+        <v>2067</v>
+      </c>
+      <c r="E97" s="172" t="s">
+        <v>2068</v>
+      </c>
+      <c r="F97" s="172" t="s">
+        <v>2069</v>
+      </c>
+      <c r="G97" s="175"/>
+      <c r="H97" s="175"/>
+    </row>
+    <row r="98" spans="4:8">
+      <c r="D98" s="171" t="s">
+        <v>2070</v>
+      </c>
+      <c r="E98" s="172" t="s">
+        <v>2071</v>
+      </c>
+      <c r="F98" s="172" t="s">
+        <v>2072</v>
+      </c>
+      <c r="G98" s="175"/>
+      <c r="H98" s="175"/>
+    </row>
+    <row r="99" spans="4:8">
+      <c r="D99" s="171" t="s">
+        <v>2073</v>
+      </c>
+      <c r="E99" s="172" t="s">
+        <v>2074</v>
+      </c>
+      <c r="F99" s="172" t="s">
+        <v>2075</v>
+      </c>
+      <c r="G99" s="175"/>
+      <c r="H99" s="175"/>
+    </row>
+    <row r="100" spans="4:8">
+      <c r="D100" s="171" t="s">
+        <v>2076</v>
+      </c>
+      <c r="E100" s="172" t="s">
+        <v>2077</v>
+      </c>
+      <c r="F100" s="172" t="s">
+        <v>2078</v>
+      </c>
+      <c r="G100" s="175"/>
+      <c r="H100" s="175"/>
+    </row>
+    <row r="101" spans="4:8">
+      <c r="D101" s="173" t="s">
+        <v>2079</v>
+      </c>
+      <c r="E101" s="175"/>
+      <c r="F101" s="175"/>
+      <c r="G101" s="175"/>
+      <c r="H101" s="175"/>
+    </row>
+    <row r="102" spans="4:8">
+      <c r="D102" s="175"/>
+      <c r="E102" s="175"/>
+      <c r="F102" s="175"/>
+      <c r="G102" s="175"/>
+      <c r="H102" s="175"/>
+    </row>
+    <row r="103" spans="4:8">
+      <c r="D103" s="175"/>
+      <c r="E103" s="175"/>
+      <c r="F103" s="175"/>
+      <c r="G103" s="175"/>
+      <c r="H103" s="175"/>
+    </row>
+    <row r="104" spans="4:8" ht="17.25">
+      <c r="D104" s="181" t="s">
+        <v>2080</v>
+      </c>
+      <c r="E104" s="175"/>
+      <c r="F104" s="175"/>
+      <c r="G104" s="175"/>
+      <c r="H104" s="175"/>
+    </row>
+    <row r="105" spans="4:8">
+      <c r="D105" s="171" t="s">
+        <v>2081</v>
+      </c>
+      <c r="E105" s="175"/>
+      <c r="F105" s="175"/>
+      <c r="G105" s="175"/>
+      <c r="H105" s="175"/>
+    </row>
+    <row r="106" spans="4:8">
+      <c r="D106" s="170" t="s">
+        <v>2082</v>
+      </c>
+      <c r="E106" s="170" t="s">
+        <v>2083</v>
+      </c>
+      <c r="F106" s="170" t="s">
+        <v>2084</v>
+      </c>
+      <c r="G106" s="170" t="s">
+        <v>2085</v>
+      </c>
+      <c r="H106" s="170" t="s">
+        <v>2086</v>
+      </c>
+    </row>
+    <row r="107" spans="4:8">
+      <c r="D107" s="173" t="s">
+        <v>2087</v>
+      </c>
+      <c r="E107" s="172">
+        <v>1782</v>
+      </c>
+      <c r="F107" s="172" t="s">
+        <v>2088</v>
+      </c>
+      <c r="G107" s="172" t="s">
+        <v>2089</v>
+      </c>
+      <c r="H107" s="172" t="s">
+        <v>2090</v>
+      </c>
+    </row>
+    <row r="108" spans="4:8">
+      <c r="D108" s="173" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E108" s="172">
+        <v>870</v>
+      </c>
+      <c r="F108" s="172" t="s">
+        <v>2092</v>
+      </c>
+      <c r="G108" s="172">
+        <v>0</v>
+      </c>
+      <c r="H108" s="172" t="s">
+        <v>2093</v>
+      </c>
+    </row>
+    <row r="109" spans="4:8">
+      <c r="D109" s="173" t="s">
+        <v>2094</v>
+      </c>
+      <c r="E109" s="172">
+        <v>312</v>
+      </c>
+      <c r="F109" s="172" t="s">
+        <v>2095</v>
+      </c>
+      <c r="G109" s="172" t="s">
+        <v>2096</v>
+      </c>
+      <c r="H109" s="172" t="s">
+        <v>2097</v>
+      </c>
+    </row>
+    <row r="110" spans="4:8">
+      <c r="D110" s="173" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E110" s="172">
+        <v>628</v>
+      </c>
+      <c r="F110" s="172" t="s">
+        <v>2099</v>
+      </c>
+      <c r="G110" s="172" t="s">
+        <v>2096</v>
+      </c>
+      <c r="H110" s="172" t="s">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="111" spans="4:8">
+      <c r="D111" s="171" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E111" s="175"/>
+      <c r="F111" s="175"/>
+      <c r="G111" s="175"/>
+      <c r="H111" s="175"/>
+    </row>
+    <row r="112" spans="4:8">
+      <c r="D112" s="171" t="s">
+        <v>2116</v>
+      </c>
+      <c r="E112" s="175"/>
+      <c r="F112" s="175"/>
+      <c r="G112" s="175"/>
+      <c r="H112" s="175"/>
+    </row>
+    <row r="113" spans="4:8">
+      <c r="D113" s="175"/>
+      <c r="E113" s="175"/>
+      <c r="F113" s="175"/>
+      <c r="G113" s="175"/>
+      <c r="H113" s="175"/>
+    </row>
+    <row r="114" spans="4:8">
+      <c r="D114" s="175"/>
+      <c r="E114" s="175"/>
+      <c r="F114" s="175"/>
+      <c r="G114" s="175"/>
+      <c r="H114" s="175"/>
+    </row>
+    <row r="115" spans="4:8" ht="17.25">
+      <c r="D115" s="181" t="s">
+        <v>2101</v>
+      </c>
+      <c r="E115" s="175"/>
+      <c r="F115" s="175"/>
+      <c r="G115" s="175"/>
+      <c r="H115" s="175"/>
+    </row>
+    <row r="116" spans="4:8">
+      <c r="D116" s="173" t="s">
+        <v>2102</v>
+      </c>
+      <c r="E116" s="175"/>
+      <c r="F116" s="175"/>
+      <c r="G116" s="175"/>
+      <c r="H116" s="175"/>
+    </row>
+    <row r="117" spans="4:8">
+      <c r="D117" s="176"/>
+      <c r="E117" s="175"/>
+      <c r="F117" s="175"/>
+      <c r="G117" s="175"/>
+      <c r="H117" s="175"/>
+    </row>
+    <row r="118" spans="4:8">
+      <c r="D118" s="178" t="s">
+        <v>2103</v>
+      </c>
+      <c r="E118" s="175"/>
+      <c r="F118" s="175"/>
+      <c r="G118" s="175"/>
+      <c r="H118" s="175"/>
+    </row>
+    <row r="119" spans="4:8">
+      <c r="D119" s="178" t="s">
+        <v>2104</v>
+      </c>
+      <c r="E119" s="175"/>
+      <c r="F119" s="175"/>
+      <c r="G119" s="175"/>
+      <c r="H119" s="175"/>
+    </row>
+    <row r="120" spans="4:8">
+      <c r="D120" s="178" t="s">
+        <v>2105</v>
+      </c>
+      <c r="E120" s="175"/>
+      <c r="F120" s="175"/>
+      <c r="G120" s="175"/>
+      <c r="H120" s="175"/>
+    </row>
+    <row r="121" spans="4:8">
+      <c r="D121" s="178" t="s">
+        <v>2106</v>
+      </c>
+      <c r="E121" s="175"/>
+      <c r="F121" s="175"/>
+      <c r="G121" s="175"/>
+      <c r="H121" s="175"/>
+    </row>
+    <row r="122" spans="4:8">
+      <c r="D122" s="175"/>
+      <c r="E122" s="175"/>
+      <c r="F122" s="175"/>
+      <c r="G122" s="175"/>
+      <c r="H122" s="175"/>
+    </row>
+    <row r="123" spans="4:8">
+      <c r="D123" s="171" t="s">
+        <v>2117</v>
+      </c>
+      <c r="E123" s="175"/>
+      <c r="F123" s="175"/>
+      <c r="G123" s="175"/>
+      <c r="H123" s="175"/>
+    </row>
+    <row r="124" spans="4:8">
+      <c r="D124" s="171" t="s">
+        <v>2107</v>
+      </c>
+      <c r="E124" s="175"/>
+      <c r="F124" s="175"/>
+      <c r="G124" s="175"/>
+      <c r="H124" s="175"/>
+    </row>
+    <row r="125" spans="4:8">
+      <c r="D125" s="176"/>
+      <c r="E125" s="175"/>
+      <c r="F125" s="175"/>
+      <c r="G125" s="175"/>
+      <c r="H125" s="175"/>
+    </row>
+    <row r="126" spans="4:8">
+      <c r="D126" s="178" t="s">
+        <v>2108</v>
+      </c>
+      <c r="E126" s="175"/>
+      <c r="F126" s="175"/>
+      <c r="G126" s="175"/>
+      <c r="H126" s="175"/>
+    </row>
+    <row r="127" spans="4:8">
+      <c r="D127" s="182" t="s">
+        <v>2118</v>
+      </c>
+      <c r="E127" s="175"/>
+      <c r="F127" s="175"/>
+      <c r="G127" s="175"/>
+      <c r="H127" s="175"/>
+    </row>
+    <row r="128" spans="4:8">
+      <c r="D128" s="178" t="s">
+        <v>2109</v>
+      </c>
+      <c r="E128" s="175"/>
+      <c r="F128" s="175"/>
+      <c r="G128" s="175"/>
+      <c r="H128" s="175"/>
+    </row>
+    <row r="129" spans="4:8">
+      <c r="D129" s="175"/>
+      <c r="E129" s="175"/>
+      <c r="F129" s="175"/>
+      <c r="G129" s="175"/>
+      <c r="H129" s="175"/>
+    </row>
+    <row r="130" spans="4:8">
+      <c r="D130" s="175"/>
+      <c r="E130" s="175"/>
+      <c r="F130" s="175"/>
+      <c r="G130" s="175"/>
+      <c r="H130" s="175"/>
+    </row>
+    <row r="131" spans="4:8">
+      <c r="D131" s="175"/>
+      <c r="E131" s="175"/>
+      <c r="F131" s="175"/>
+      <c r="G131" s="175"/>
+      <c r="H131" s="175"/>
+    </row>
+    <row r="132" spans="4:8" ht="17.25">
+      <c r="D132" s="181" t="s">
+        <v>2110</v>
+      </c>
+      <c r="E132" s="175"/>
+      <c r="F132" s="175"/>
+      <c r="G132" s="175"/>
+      <c r="H132" s="175"/>
+    </row>
+    <row r="133" spans="4:8">
+      <c r="D133" s="171" t="s">
+        <v>2111</v>
+      </c>
+      <c r="E133" s="175"/>
+      <c r="F133" s="175"/>
+      <c r="G133" s="175"/>
+      <c r="H133" s="175"/>
+    </row>
+    <row r="134" spans="4:8">
+      <c r="D134" s="173" t="s">
+        <v>2112</v>
+      </c>
+      <c r="E134" s="175"/>
+      <c r="F134" s="175"/>
+      <c r="G134" s="175"/>
+      <c r="H134" s="175"/>
+    </row>
+    <row r="136" spans="4:8">
+      <c r="D136" t="s">
+        <v>2119</v>
+      </c>
+    </row>
+    <row r="137" spans="4:8">
+      <c r="D137" t="s">
+        <v>2120</v>
+      </c>
+    </row>
+    <row r="138" spans="4:8">
+      <c r="D138" t="s">
+        <v>2121</v>
+      </c>
+    </row>
+    <row r="139" spans="4:8">
+      <c r="D139" t="s">
+        <v>2122</v>
+      </c>
+    </row>
+    <row r="140" spans="4:8">
+      <c r="D140" t="s">
+        <v>2123</v>
+      </c>
+    </row>
+    <row r="141" spans="4:8">
+      <c r="D141" t="s">
+        <v>2124</v>
+      </c>
+    </row>
+    <row r="142" spans="4:8">
+      <c r="D142" t="s">
+        <v>2125</v>
+      </c>
+    </row>
+    <row r="143" spans="4:8">
+      <c r="D143" t="s">
+        <v>2126</v>
+      </c>
+    </row>
+    <row r="144" spans="4:8">
+      <c r="D144" t="s">
+        <v>2127</v>
+      </c>
+    </row>
+    <row r="146" spans="4:4">
+      <c r="D146" s="8" t="s">
+        <v>2128</v>
+      </c>
+    </row>
+    <row r="147" spans="4:4" ht="28.5">
+      <c r="D147" s="7" t="s">
+        <v>2129</v>
+      </c>
+    </row>
+    <row r="149" spans="4:4">
+      <c r="D149" t="s">
+        <v>2130</v>
+      </c>
+    </row>
+    <row r="150" spans="4:4">
+      <c r="D150" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="151" spans="4:4">
+      <c r="D151" t="s">
+        <v>2132</v>
+      </c>
+    </row>
+    <row r="152" spans="4:4">
+      <c r="D152" t="s">
+        <v>2133</v>
+      </c>
+    </row>
+    <row r="153" spans="4:4">
+      <c r="D153" t="s">
+        <v>2134</v>
+      </c>
+    </row>
+    <row r="154" spans="4:4">
+      <c r="D154" t="s">
+        <v>2127</v>
+      </c>
+    </row>
+    <row r="156" spans="4:4">
+      <c r="D156" t="s">
+        <v>2135</v>
+      </c>
+    </row>
+    <row r="157" spans="4:4">
+      <c r="D157" t="s">
+        <v>2136</v>
+      </c>
+    </row>
+    <row r="158" spans="4:4">
+      <c r="D158" t="s">
+        <v>2132</v>
+      </c>
+    </row>
+    <row r="159" spans="4:4">
+      <c r="D159" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="160" spans="4:4">
+      <c r="D160" t="s">
+        <v>2138</v>
+      </c>
+    </row>
+    <row r="161" spans="4:4">
+      <c r="D161" t="s">
+        <v>2139</v>
+      </c>
+    </row>
+    <row r="162" spans="4:4">
+      <c r="D162" t="s">
+        <v>2140</v>
+      </c>
+    </row>
+    <row r="163" spans="4:4">
+      <c r="D163" t="s">
+        <v>2141</v>
+      </c>
+    </row>
+    <row r="164" spans="4:4">
+      <c r="D164" t="s">
+        <v>2127</v>
+      </c>
+    </row>
+    <row r="166" spans="4:4">
+      <c r="D166" t="s">
+        <v>2142</v>
+      </c>
+    </row>
+    <row r="167" spans="4:4">
+      <c r="D167" t="s">
+        <v>2143</v>
+      </c>
+    </row>
+    <row r="168" spans="4:4">
+      <c r="D168" t="s">
+        <v>2144</v>
+      </c>
+    </row>
+    <row r="169" spans="4:4">
+      <c r="D169" t="s">
+        <v>2145</v>
+      </c>
+    </row>
+    <row r="170" spans="4:4">
+      <c r="D170" t="s">
+        <v>2146</v>
+      </c>
+    </row>
+    <row r="171" spans="4:4">
+      <c r="D171" t="s">
+        <v>2127</v>
+      </c>
+    </row>
+    <row r="173" spans="4:4">
+      <c r="D173" s="14" t="s">
+        <v>2147</v>
+      </c>
+    </row>
+    <row r="174" spans="4:4">
+      <c r="D174" s="169"/>
+    </row>
+    <row r="175" spans="4:4">
+      <c r="D175" s="169"/>
+    </row>
+    <row r="176" spans="4:4">
+      <c r="D176" s="14" t="s">
+        <v>2148</v>
+      </c>
+    </row>
+    <row r="177" spans="4:4">
+      <c r="D177" s="37" t="s">
+        <v>2150</v>
+      </c>
+    </row>
+    <row r="178" spans="4:4">
+      <c r="D178" s="37" t="s">
+        <v>2149</v>
+      </c>
+    </row>
+    <row r="180" spans="4:4">
+      <c r="D180" t="s">
+        <v>2151</v>
+      </c>
+    </row>
+    <row r="181" spans="4:4">
+      <c r="D181" t="s">
+        <v>2152</v>
+      </c>
+    </row>
+    <row r="182" spans="4:4">
+      <c r="D182" t="s">
+        <v>2153</v>
+      </c>
+    </row>
+    <row r="183" spans="4:4">
+      <c r="D183" t="s">
+        <v>2154</v>
+      </c>
+    </row>
+    <row r="184" spans="4:4">
+      <c r="D184" t="s">
+        <v>2155</v>
+      </c>
+    </row>
+    <row r="185" spans="4:4">
+      <c r="D185" t="s">
+        <v>2156</v>
+      </c>
+    </row>
+    <row r="186" spans="4:4">
+      <c r="D186" t="s">
+        <v>2157</v>
+      </c>
+    </row>
+    <row r="187" spans="4:4">
+      <c r="D187" t="s">
+        <v>2151</v>
+      </c>
+    </row>
+    <row r="189" spans="4:4">
+      <c r="D189" t="s">
+        <v>2158</v>
+      </c>
+    </row>
+    <row r="190" spans="4:4">
+      <c r="D190" t="s">
+        <v>2159</v>
+      </c>
+    </row>
+    <row r="191" spans="4:4">
+      <c r="D191" t="s">
+        <v>2160</v>
+      </c>
+    </row>
+    <row r="192" spans="4:4">
+      <c r="D192" t="s">
+        <v>2161</v>
+      </c>
+    </row>
+    <row r="193" spans="4:4">
+      <c r="D193" t="s">
+        <v>2162</v>
+      </c>
+    </row>
+    <row r="194" spans="4:4">
+      <c r="D194" t="s">
+        <v>2163</v>
+      </c>
+    </row>
+    <row r="195" spans="4:4">
+      <c r="D195" t="s">
+        <v>2164</v>
+      </c>
+    </row>
+    <row r="196" spans="4:4">
+      <c r="D196" t="s">
+        <v>2165</v>
+      </c>
+    </row>
+    <row r="197" spans="4:4">
+      <c r="D197" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="198" spans="4:4">
+      <c r="D198" t="s">
+        <v>2167</v>
+      </c>
+    </row>
+    <row r="199" spans="4:4">
+      <c r="D199" t="s">
+        <v>2168</v>
+      </c>
+    </row>
+    <row r="200" spans="4:4">
+      <c r="D200" t="s">
+        <v>2169</v>
+      </c>
+    </row>
+    <row r="201" spans="4:4">
+      <c r="D201" t="s">
+        <v>2170</v>
+      </c>
+    </row>
+    <row r="202" spans="4:4">
+      <c r="D202" t="s">
+        <v>2171</v>
+      </c>
+    </row>
+    <row r="203" spans="4:4">
+      <c r="D203" t="s">
+        <v>2167</v>
+      </c>
+    </row>
+    <row r="204" spans="4:4">
+      <c r="D204" t="s">
+        <v>2172</v>
+      </c>
+    </row>
+    <row r="205" spans="4:4">
+      <c r="D205" t="s">
+        <v>2173</v>
+      </c>
+    </row>
+    <row r="206" spans="4:4">
+      <c r="D206" t="s">
+        <v>2174</v>
+      </c>
+    </row>
+    <row r="207" spans="4:4">
+      <c r="D207" t="s">
+        <v>2175</v>
+      </c>
+    </row>
+    <row r="208" spans="4:4">
+      <c r="D208" t="s">
+        <v>2176</v>
+      </c>
+    </row>
+    <row r="209" spans="4:4">
+      <c r="D209" t="s">
+        <v>2177</v>
+      </c>
+    </row>
+    <row r="210" spans="4:4">
+      <c r="D210" t="s">
+        <v>2178</v>
+      </c>
+    </row>
+    <row r="211" spans="4:4">
+      <c r="D211" t="s">
+        <v>2179</v>
+      </c>
+    </row>
+    <row r="212" spans="4:4">
+      <c r="D212" t="s">
+        <v>2180</v>
+      </c>
+    </row>
+    <row r="213" spans="4:4">
+      <c r="D213" t="s">
+        <v>2181</v>
+      </c>
+    </row>
+    <row r="214" spans="4:4">
+      <c r="D214" t="s">
+        <v>2182</v>
+      </c>
+    </row>
+    <row r="215" spans="4:4">
+      <c r="D215" t="s">
+        <v>2183</v>
+      </c>
+    </row>
+    <row r="217" spans="4:4">
+      <c r="D217" t="s">
+        <v>2184</v>
+      </c>
+    </row>
+    <row r="218" spans="4:4">
+      <c r="D218" t="s">
+        <v>2185</v>
+      </c>
+    </row>
+    <row r="220" spans="4:4">
+      <c r="D220" t="s">
+        <v>2186</v>
+      </c>
+    </row>
+    <row r="221" spans="4:4">
+      <c r="D221" t="s">
+        <v>2187</v>
+      </c>
+    </row>
+    <row r="223" spans="4:4">
+      <c r="D223" t="s">
+        <v>2188</v>
+      </c>
+    </row>
+    <row r="224" spans="4:4">
+      <c r="D224" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="225" spans="4:4">
+      <c r="D225" t="s">
+        <v>2190</v>
+      </c>
+    </row>
+    <row r="227" spans="4:4">
+      <c r="D227" t="s">
+        <v>2191</v>
+      </c>
+    </row>
+    <row r="228" spans="4:4">
+      <c r="D228" t="s">
+        <v>2192</v>
+      </c>
+    </row>
+    <row r="230" spans="4:4">
+      <c r="D230" t="s">
+        <v>2193</v>
+      </c>
+    </row>
+    <row r="231" spans="4:4">
+      <c r="D231" t="s">
+        <v>2194</v>
+      </c>
+    </row>
+    <row r="233" spans="4:4">
+      <c r="D233" t="s">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="234" spans="4:4">
+      <c r="D234" t="s">
+        <v>2196</v>
+      </c>
+    </row>
+    <row r="236" spans="4:4">
+      <c r="D236" t="s">
+        <v>2197</v>
+      </c>
+    </row>
+    <row r="237" spans="4:4">
+      <c r="D237" t="s">
+        <v>2198</v>
+      </c>
+    </row>
+    <row r="238" spans="4:4">
+      <c r="D238" t="s">
+        <v>2199</v>
+      </c>
+    </row>
+    <row r="240" spans="4:4">
+      <c r="D240" t="s">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="241" spans="4:4">
+      <c r="D241" t="s">
+        <v>2201</v>
+      </c>
+    </row>
+    <row r="243" spans="4:4">
+      <c r="D243" t="s">
+        <v>2202</v>
+      </c>
+    </row>
+    <row r="244" spans="4:4">
+      <c r="D244" t="s">
+        <v>2203</v>
+      </c>
+    </row>
+    <row r="246" spans="4:4">
+      <c r="D246" t="s">
+        <v>2204</v>
+      </c>
+    </row>
+    <row r="248" spans="4:4">
+      <c r="D248" s="37" t="s">
+        <v>2223</v>
+      </c>
+    </row>
+    <row r="249" spans="4:4">
+      <c r="D249" s="169"/>
+    </row>
+    <row r="250" spans="4:4">
+      <c r="D250" s="169"/>
+    </row>
+    <row r="251" spans="4:4">
+      <c r="D251" s="37" t="s">
+        <v>2205</v>
+      </c>
+    </row>
+    <row r="252" spans="4:4">
+      <c r="D252" s="37" t="s">
+        <v>2206</v>
+      </c>
+    </row>
+    <row r="253" spans="4:4">
+      <c r="D253" s="38"/>
+    </row>
+    <row r="254" spans="4:4">
+      <c r="D254" s="40" t="s">
+        <v>2207</v>
+      </c>
+    </row>
+    <row r="255" spans="4:4">
+      <c r="D255" s="39" t="s">
+        <v>2208</v>
+      </c>
+    </row>
+    <row r="256" spans="4:4">
+      <c r="D256" s="39" t="s">
+        <v>2209</v>
+      </c>
+    </row>
+    <row r="257" spans="4:4">
+      <c r="D257" s="169"/>
+    </row>
+    <row r="258" spans="4:4">
+      <c r="D258" s="37" t="s">
+        <v>2210</v>
+      </c>
+    </row>
+    <row r="259" spans="4:4">
+      <c r="D259" s="38"/>
+    </row>
+    <row r="260" spans="4:4">
+      <c r="D260" s="39" t="s">
+        <v>2224</v>
+      </c>
+    </row>
+    <row r="261" spans="4:4">
+      <c r="D261" s="39" t="s">
+        <v>2211</v>
+      </c>
+    </row>
+    <row r="262" spans="4:4">
+      <c r="D262" s="39" t="s">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="263" spans="4:4">
+      <c r="D263" s="169"/>
+    </row>
+    <row r="264" spans="4:4">
+      <c r="D264" s="37" t="s">
+        <v>2213</v>
+      </c>
+    </row>
+    <row r="265" spans="4:4">
+      <c r="D265" s="38"/>
+    </row>
+    <row r="266" spans="4:4">
+      <c r="D266" s="39" t="s">
+        <v>2225</v>
+      </c>
+    </row>
+    <row r="267" spans="4:4">
+      <c r="D267" s="40" t="s">
+        <v>2214</v>
+      </c>
+    </row>
+    <row r="268" spans="4:4">
+      <c r="D268" s="40" t="s">
+        <v>2215</v>
+      </c>
+    </row>
+    <row r="269" spans="4:4">
+      <c r="D269" s="169"/>
+    </row>
+    <row r="270" spans="4:4">
+      <c r="D270" s="37" t="s">
+        <v>2216</v>
+      </c>
+    </row>
+    <row r="271" spans="4:4">
+      <c r="D271" s="38"/>
+    </row>
+    <row r="272" spans="4:4">
+      <c r="D272" s="39" t="s">
+        <v>2226</v>
+      </c>
+    </row>
+    <row r="273" spans="4:4">
+      <c r="D273" s="40" t="s">
+        <v>2217</v>
+      </c>
+    </row>
+    <row r="274" spans="4:4">
+      <c r="D274" s="39" t="s">
+        <v>2218</v>
+      </c>
+    </row>
+    <row r="275" spans="4:4">
+      <c r="D275" s="169"/>
+    </row>
+    <row r="276" spans="4:4">
+      <c r="D276" s="37" t="s">
+        <v>2219</v>
+      </c>
+    </row>
+    <row r="277" spans="4:4">
+      <c r="D277" s="38"/>
+    </row>
+    <row r="278" spans="4:4">
+      <c r="D278" s="39" t="s">
+        <v>2227</v>
+      </c>
+    </row>
+    <row r="279" spans="4:4">
+      <c r="D279" s="39" t="s">
+        <v>2228</v>
+      </c>
+    </row>
+    <row r="280" spans="4:4">
+      <c r="D280" s="40" t="s">
+        <v>2220</v>
+      </c>
+    </row>
+    <row r="281" spans="4:4">
+      <c r="D281" s="169"/>
+    </row>
+    <row r="282" spans="4:4">
+      <c r="D282" s="169"/>
+    </row>
+    <row r="283" spans="4:4">
+      <c r="D283" s="169"/>
+    </row>
+    <row r="284" spans="4:4">
+      <c r="D284" s="37" t="s">
+        <v>2221</v>
+      </c>
+    </row>
+    <row r="285" spans="4:4">
+      <c r="D285" s="14" t="s">
+        <v>2222</v>
+      </c>
+    </row>
+    <row r="287" spans="4:4">
+      <c r="D287" t="s">
+        <v>2229</v>
+      </c>
+    </row>
+    <row r="288" spans="4:4">
+      <c r="D288" t="s">
+        <v>2230</v>
+      </c>
+    </row>
+    <row r="289" spans="4:4">
+      <c r="D289" t="s">
+        <v>2231</v>
+      </c>
+    </row>
+    <row r="290" spans="4:4">
+      <c r="D290" t="s">
+        <v>2232</v>
+      </c>
+    </row>
+    <row r="291" spans="4:4">
+      <c r="D291" t="s">
+        <v>2233</v>
+      </c>
+    </row>
+    <row r="292" spans="4:4">
+      <c r="D292" t="s">
+        <v>2234</v>
+      </c>
+    </row>
+    <row r="293" spans="4:4">
+      <c r="D293" t="s">
+        <v>2235</v>
+      </c>
+    </row>
+    <row r="294" spans="4:4">
+      <c r="D294" t="s">
+        <v>2236</v>
+      </c>
+    </row>
+    <row r="295" spans="4:4">
+      <c r="D295" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="296" spans="4:4">
+      <c r="D296" t="s">
+        <v>2238</v>
+      </c>
+    </row>
+    <row r="298" spans="4:4">
+      <c r="D298" s="14" t="s">
+        <v>2239</v>
+      </c>
+    </row>
+    <row r="300" spans="4:4">
+      <c r="D300" t="s">
+        <v>2240</v>
+      </c>
+    </row>
+    <row r="301" spans="4:4">
+      <c r="D301" t="s">
+        <v>2241</v>
+      </c>
+    </row>
+    <row r="302" spans="4:4">
+      <c r="D302" t="s">
+        <v>2242</v>
+      </c>
+    </row>
+    <row r="303" spans="4:4">
+      <c r="D303" t="s">
+        <v>2243</v>
+      </c>
+    </row>
+    <row r="304" spans="4:4">
+      <c r="D304" t="s">
+        <v>2244</v>
+      </c>
+    </row>
+    <row r="305" spans="4:4">
+      <c r="D305" t="s">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="306" spans="4:4">
+      <c r="D306" t="s">
+        <v>2246</v>
+      </c>
+    </row>
+    <row r="307" spans="4:4">
+      <c r="D307" t="s">
+        <v>2247</v>
+      </c>
+    </row>
+    <row r="309" spans="4:4">
+      <c r="D309" s="14" t="s">
+        <v>2248</v>
+      </c>
+    </row>
+    <row r="311" spans="4:4">
+      <c r="D311" t="s">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="313" spans="4:4">
+      <c r="D313" s="14" t="s">
+        <v>2250</v>
+      </c>
+    </row>
+    <row r="315" spans="4:4">
+      <c r="D315" t="s">
+        <v>2251</v>
+      </c>
+    </row>
+    <row r="316" spans="4:4">
+      <c r="D316" t="s">
+        <v>2252</v>
+      </c>
+    </row>
+    <row r="318" spans="4:4">
+      <c r="D318" s="7" t="s">
+        <v>2255</v>
+      </c>
+    </row>
+    <row r="319" spans="4:4">
+      <c r="D319" s="5"/>
+    </row>
+    <row r="320" spans="4:4">
+      <c r="D320" s="5"/>
+    </row>
+    <row r="321" spans="4:4">
+      <c r="D321" s="7" t="s">
+        <v>2253</v>
+      </c>
+    </row>
+    <row r="322" spans="4:4">
+      <c r="D322" s="7" t="s">
+        <v>2254</v>
+      </c>
+    </row>
+    <row r="324" spans="4:4">
+      <c r="D324" t="s">
+        <v>2256</v>
+      </c>
+    </row>
+    <row r="326" spans="4:4">
+      <c r="D326" s="7" t="s">
+        <v>2257</v>
+      </c>
+    </row>
+    <row r="327" spans="4:4">
+      <c r="D327" s="20"/>
+    </row>
+    <row r="328" spans="4:4">
+      <c r="D328" s="21" t="s">
+        <v>2258</v>
+      </c>
+    </row>
+    <row r="329" spans="4:4">
+      <c r="D329" s="21" t="s">
+        <v>2259</v>
+      </c>
+    </row>
+    <row r="330" spans="4:4">
+      <c r="D330" s="5"/>
+    </row>
+    <row r="331" spans="4:4">
+      <c r="D331" s="7" t="s">
+        <v>2260</v>
+      </c>
+    </row>
+    <row r="332" spans="4:4">
+      <c r="D332" s="20"/>
+    </row>
+    <row r="333" spans="4:4">
+      <c r="D333" s="21" t="s">
+        <v>2261</v>
+      </c>
+    </row>
+    <row r="334" spans="4:4">
+      <c r="D334" s="21" t="s">
+        <v>2262</v>
+      </c>
+    </row>
+    <row r="335" spans="4:4">
+      <c r="D335" s="21" t="s">
+        <v>2263</v>
+      </c>
+    </row>
+    <row r="336" spans="4:4">
+      <c r="D336" s="5"/>
+    </row>
+    <row r="337" spans="4:4">
+      <c r="D337" s="7" t="s">
+        <v>2264</v>
+      </c>
+    </row>
+    <row r="339" spans="4:4">
+      <c r="D339" t="s">
+        <v>2265</v>
+      </c>
+    </row>
+    <row r="340" spans="4:4">
+      <c r="D340" t="s">
+        <v>2266</v>
+      </c>
+    </row>
+    <row r="341" spans="4:4">
+      <c r="D341" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="342" spans="4:4">
+      <c r="D342" t="s">
+        <v>2167</v>
+      </c>
+    </row>
+    <row r="343" spans="4:4">
+      <c r="D343" t="s">
+        <v>2268</v>
+      </c>
+    </row>
+    <row r="344" spans="4:4">
+      <c r="D344" t="s">
+        <v>2269</v>
+      </c>
+    </row>
+    <row r="345" spans="4:4">
+      <c r="D345" t="s">
+        <v>2270</v>
+      </c>
+    </row>
+    <row r="346" spans="4:4">
+      <c r="D346" t="s">
+        <v>2271</v>
+      </c>
+    </row>
+    <row r="347" spans="4:4">
+      <c r="D347" t="s">
+        <v>2272</v>
+      </c>
+    </row>
+    <row r="348" spans="4:4">
+      <c r="D348" t="s">
+        <v>2273</v>
+      </c>
+    </row>
+    <row r="349" spans="4:4">
+      <c r="D349" t="s">
+        <v>2274</v>
+      </c>
+    </row>
+    <row r="350" spans="4:4">
+      <c r="D350" t="s">
+        <v>2167</v>
+      </c>
+    </row>
+    <row r="351" spans="4:4">
+      <c r="D351" t="s">
+        <v>2275</v>
+      </c>
+    </row>
+    <row r="352" spans="4:4">
+      <c r="D352" t="s">
+        <v>2276</v>
+      </c>
+    </row>
+    <row r="353" spans="4:4">
+      <c r="D353" t="s">
+        <v>2277</v>
+      </c>
+    </row>
+    <row r="354" spans="4:4">
+      <c r="D354" t="s">
+        <v>2278</v>
+      </c>
+    </row>
+    <row r="355" spans="4:4">
+      <c r="D355" t="s">
+        <v>2279</v>
+      </c>
+    </row>
+    <row r="356" spans="4:4">
+      <c r="D356" t="s">
+        <v>2167</v>
+      </c>
+    </row>
+    <row r="357" spans="4:4">
+      <c r="D357" t="s">
+        <v>2280</v>
+      </c>
+    </row>
+    <row r="358" spans="4:4">
+      <c r="D358" t="s">
+        <v>2281</v>
+      </c>
+    </row>
+    <row r="359" spans="4:4">
+      <c r="D359" t="s">
+        <v>2282</v>
+      </c>
+    </row>
+    <row r="360" spans="4:4">
+      <c r="D360" t="s">
+        <v>2283</v>
+      </c>
+    </row>
+    <row r="361" spans="4:4">
+      <c r="D361" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="362" spans="4:4">
+      <c r="D362" t="s">
+        <v>2167</v>
+      </c>
+    </row>
+    <row r="363" spans="4:4">
+      <c r="D363" t="s">
+        <v>2285</v>
+      </c>
+    </row>
+    <row r="364" spans="4:4">
+      <c r="D364" t="s">
+        <v>2183</v>
+      </c>
+    </row>
+    <row r="366" spans="4:4">
+      <c r="D366" s="4" t="s">
+        <v>2286</v>
+      </c>
+    </row>
+    <row r="368" spans="4:4">
+      <c r="D368" t="s">
+        <v>2287</v>
+      </c>
+    </row>
+    <row r="369" spans="4:4">
+      <c r="D369" t="s">
+        <v>2288</v>
+      </c>
+    </row>
+    <row r="370" spans="4:4">
+      <c r="D370" t="s">
+        <v>2289</v>
+      </c>
+    </row>
+    <row r="371" spans="4:4">
+      <c r="D371" t="s">
+        <v>2290</v>
+      </c>
+    </row>
+    <row r="373" spans="4:4" ht="17.25">
+      <c r="D373" s="157" t="s">
+        <v>2291</v>
+      </c>
+    </row>
+    <row r="374" spans="4:4">
+      <c r="D374" s="7" t="s">
+        <v>2292</v>
+      </c>
+    </row>
+    <row r="375" spans="4:4">
+      <c r="D375" s="7" t="s">
+        <v>2293</v>
+      </c>
+    </row>
+    <row r="377" spans="4:4">
+      <c r="D377" t="s">
+        <v>2294</v>
+      </c>
+    </row>
+    <row r="378" spans="4:4">
+      <c r="D378" t="s">
+        <v>2295</v>
+      </c>
+    </row>
+    <row r="379" spans="4:4">
+      <c r="D379" t="s">
+        <v>2296</v>
+      </c>
+    </row>
+    <row r="380" spans="4:4">
+      <c r="D380" t="s">
+        <v>2297</v>
+      </c>
+    </row>
+    <row r="381" spans="4:4">
+      <c r="D381" t="s">
+        <v>2298</v>
+      </c>
+    </row>
+    <row r="383" spans="4:4">
+      <c r="D383" t="s">
+        <v>2299</v>
+      </c>
+    </row>
+    <row r="384" spans="4:4">
+      <c r="D384" t="s">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="385" spans="4:4">
+      <c r="D385" t="s">
+        <v>2301</v>
+      </c>
+    </row>
+    <row r="386" spans="4:4">
+      <c r="D386" t="s">
+        <v>2302</v>
+      </c>
+    </row>
+    <row r="387" spans="4:4">
+      <c r="D387" t="s">
+        <v>2303</v>
+      </c>
+    </row>
+    <row r="388" spans="4:4">
+      <c r="D388" t="s">
+        <v>2304</v>
+      </c>
+    </row>
+    <row r="389" spans="4:4">
+      <c r="D389" t="s">
+        <v>2305</v>
+      </c>
+    </row>
+    <row r="391" spans="4:4">
+      <c r="D391" s="4" t="s">
+        <v>2306</v>
+      </c>
+    </row>
+    <row r="393" spans="4:4">
+      <c r="D393" t="s">
+        <v>2307</v>
+      </c>
+    </row>
+    <row r="394" spans="4:4">
+      <c r="D394" t="s">
+        <v>2308</v>
+      </c>
+    </row>
+    <row r="395" spans="4:4">
+      <c r="D395" t="s">
+        <v>2309</v>
+      </c>
+    </row>
+    <row r="397" spans="4:4">
+      <c r="D397" t="s">
+        <v>2310</v>
+      </c>
+    </row>
+    <row r="398" spans="4:4">
+      <c r="D398" t="s">
+        <v>2311</v>
+      </c>
+    </row>
+    <row r="399" spans="4:4">
+      <c r="D399" t="s">
+        <v>2312</v>
+      </c>
+    </row>
+    <row r="400" spans="4:4">
+      <c r="D400" t="s">
+        <v>2313</v>
+      </c>
+    </row>
+    <row r="401" spans="4:4">
+      <c r="D401" t="s">
+        <v>2314</v>
+      </c>
+    </row>
+    <row r="403" spans="4:4">
+      <c r="D403" s="4" t="s">
+        <v>2315</v>
+      </c>
+    </row>
+    <row r="405" spans="4:4">
+      <c r="D405" t="s">
+        <v>2316</v>
+      </c>
+    </row>
+    <row r="406" spans="4:4">
+      <c r="D406" t="s">
+        <v>2317</v>
+      </c>
+    </row>
+    <row r="407" spans="4:4">
+      <c r="D407" t="s">
+        <v>2318</v>
+      </c>
+    </row>
+    <row r="408" spans="4:4">
+      <c r="D408" t="s">
+        <v>2319</v>
+      </c>
+    </row>
+    <row r="409" spans="4:4">
+      <c r="D409" t="s">
+        <v>2167</v>
+      </c>
+    </row>
+    <row r="410" spans="4:4">
+      <c r="D410" t="s">
+        <v>2320</v>
+      </c>
+    </row>
+    <row r="411" spans="4:4">
+      <c r="D411" t="s">
+        <v>2321</v>
+      </c>
+    </row>
+    <row r="412" spans="4:4">
+      <c r="D412" t="s">
+        <v>2322</v>
+      </c>
+    </row>
+    <row r="413" spans="4:4">
+      <c r="D413" t="s">
+        <v>2323</v>
+      </c>
+    </row>
+    <row r="414" spans="4:4">
+      <c r="D414" t="s">
+        <v>2324</v>
+      </c>
+    </row>
+    <row r="415" spans="4:4">
+      <c r="D415" t="s">
+        <v>2325</v>
+      </c>
+    </row>
+    <row r="416" spans="4:4">
+      <c r="D416" t="s">
+        <v>2167</v>
+      </c>
+    </row>
+    <row r="417" spans="4:4">
+      <c r="D417" t="s">
+        <v>2326</v>
+      </c>
+    </row>
+    <row r="418" spans="4:4">
+      <c r="D418" t="s">
+        <v>2327</v>
+      </c>
+    </row>
+    <row r="419" spans="4:4">
+      <c r="D419" t="s">
+        <v>2328</v>
+      </c>
+    </row>
+    <row r="420" spans="4:4">
+      <c r="D420" t="s">
+        <v>2329</v>
+      </c>
+    </row>
+    <row r="421" spans="4:4">
+      <c r="D421" t="s">
+        <v>2183</v>
+      </c>
+    </row>
+    <row r="423" spans="4:4">
+      <c r="D423" s="4" t="s">
+        <v>2330</v>
+      </c>
+    </row>
+    <row r="425" spans="4:4">
+      <c r="D425" t="s">
+        <v>2331</v>
+      </c>
+    </row>
+    <row r="426" spans="4:4">
+      <c r="D426" t="s">
+        <v>2332</v>
+      </c>
+    </row>
+    <row r="427" spans="4:4">
+      <c r="D427" t="s">
+        <v>2333</v>
+      </c>
+    </row>
+    <row r="428" spans="4:4">
+      <c r="D428" t="s">
+        <v>2334</v>
+      </c>
+    </row>
+    <row r="429" spans="4:4">
+      <c r="D429" t="s">
+        <v>2127</v>
+      </c>
+    </row>
+    <row r="431" spans="4:4">
+      <c r="D431" t="s">
+        <v>2335</v>
+      </c>
+    </row>
+    <row r="432" spans="4:4">
+      <c r="D432" t="s">
+        <v>2336</v>
+      </c>
+    </row>
+    <row r="433" spans="4:4">
+      <c r="D433" t="s">
+        <v>2337</v>
+      </c>
+    </row>
+    <row r="434" spans="4:4">
+      <c r="D434" t="s">
+        <v>2167</v>
+      </c>
+    </row>
+    <row r="435" spans="4:4">
+      <c r="D435" t="s">
+        <v>2338</v>
+      </c>
+    </row>
+    <row r="436" spans="4:4">
+      <c r="D436" t="s">
+        <v>2339</v>
+      </c>
+    </row>
+    <row r="437" spans="4:4">
+      <c r="D437" t="s">
+        <v>2183</v>
+      </c>
+    </row>
+    <row r="439" spans="4:4" ht="17.25">
+      <c r="D439" s="157" t="s">
+        <v>2340</v>
+      </c>
+    </row>
+    <row r="440" spans="4:4">
+      <c r="D440" s="16" t="s">
+        <v>2341</v>
+      </c>
+    </row>
+    <row r="441" spans="4:4">
+      <c r="D441" s="21"/>
+    </row>
+    <row r="442" spans="4:4">
+      <c r="D442" s="21" t="s">
+        <v>2342</v>
+      </c>
+    </row>
+    <row r="443" spans="4:4">
+      <c r="D443" s="21" t="s">
+        <v>2343</v>
+      </c>
+    </row>
+    <row r="444" spans="4:4">
+      <c r="D444" s="21" t="s">
+        <v>2344</v>
+      </c>
+    </row>
+    <row r="445" spans="4:4">
+      <c r="D445" s="21" t="s">
+        <v>2345</v>
+      </c>
+    </row>
+    <row r="446" spans="4:4">
+      <c r="D446" s="21" t="s">
+        <v>2346</v>
+      </c>
+    </row>
+    <row r="447" spans="4:4">
+      <c r="D447" s="21" t="s">
+        <v>2347</v>
+      </c>
+    </row>
+    <row r="448" spans="4:4">
+      <c r="D448" s="21" t="s">
+        <v>2348</v>
+      </c>
+    </row>
+    <row r="449" spans="4:4">
+      <c r="D449" s="21" t="s">
+        <v>2349</v>
+      </c>
+    </row>
+    <row r="450" spans="4:4">
+      <c r="D450" s="21" t="s">
+        <v>2350</v>
+      </c>
+    </row>
+    <row r="451" spans="4:4">
+      <c r="D451" s="21" t="s">
+        <v>2351</v>
+      </c>
+    </row>
+    <row r="452" spans="4:4">
+      <c r="D452" s="21" t="s">
+        <v>2352</v>
+      </c>
+    </row>
+    <row r="453" spans="4:4">
+      <c r="D453" s="21" t="s">
+        <v>2353</v>
+      </c>
+    </row>
+    <row r="454" spans="4:4">
+      <c r="D454" s="5"/>
+    </row>
+    <row r="455" spans="4:4">
+      <c r="D455" s="16" t="s">
+        <v>2354</v>
+      </c>
+    </row>
+    <row r="456" spans="4:4">
+      <c r="D456" s="21"/>
+    </row>
+    <row r="457" spans="4:4">
+      <c r="D457" s="25" t="s">
+        <v>2355</v>
+      </c>
+    </row>
+    <row r="458" spans="4:4">
+      <c r="D458" s="21" t="s">
+        <v>2356</v>
+      </c>
+    </row>
+    <row r="459" spans="4:4">
+      <c r="D459" s="21" t="s">
+        <v>2357</v>
+      </c>
+    </row>
+    <row r="460" spans="4:4">
+      <c r="D460" s="21" t="s">
+        <v>2358</v>
+      </c>
+    </row>
+    <row r="461" spans="4:4">
+      <c r="D461" s="21" t="s">
+        <v>2359</v>
+      </c>
+    </row>
+    <row r="462" spans="4:4">
+      <c r="D462" s="21" t="s">
+        <v>2360</v>
+      </c>
+    </row>
+    <row r="463" spans="4:4">
+      <c r="D463" s="21" t="s">
+        <v>2361</v>
+      </c>
+    </row>
+    <row r="464" spans="4:4">
+      <c r="D464" s="21" t="s">
+        <v>2362</v>
+      </c>
+    </row>
+    <row r="465" spans="4:4">
+      <c r="D465" s="21" t="s">
+        <v>2363</v>
+      </c>
+    </row>
+    <row r="466" spans="4:4">
+      <c r="D466" s="21" t="s">
+        <v>2364</v>
+      </c>
+    </row>
+    <row r="467" spans="4:4">
+      <c r="D467" s="21" t="s">
+        <v>2365</v>
+      </c>
+    </row>
+    <row r="468" spans="4:4">
+      <c r="D468" s="21" t="s">
+        <v>2366</v>
+      </c>
+    </row>
+    <row r="469" spans="4:4">
+      <c r="D469" s="5"/>
+    </row>
+    <row r="470" spans="4:4">
+      <c r="D470" s="16" t="s">
+        <v>2367</v>
+      </c>
+    </row>
+    <row r="471" spans="4:4">
+      <c r="D471" s="21"/>
+    </row>
+    <row r="472" spans="4:4">
+      <c r="D472" s="21" t="s">
+        <v>2368</v>
+      </c>
+    </row>
+    <row r="473" spans="4:4">
+      <c r="D473" s="21" t="s">
+        <v>2369</v>
+      </c>
+    </row>
+    <row r="474" spans="4:4">
+      <c r="D474" s="21" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="475" spans="4:4">
+      <c r="D475" s="21" t="s">
+        <v>2371</v>
+      </c>
+    </row>
+    <row r="476" spans="4:4">
+      <c r="D476" s="5"/>
+    </row>
+    <row r="477" spans="4:4">
+      <c r="D477" s="16" t="s">
+        <v>2372</v>
+      </c>
+    </row>
+    <row r="478" spans="4:4">
+      <c r="D478" s="21"/>
+    </row>
+    <row r="479" spans="4:4">
+      <c r="D479" s="21" t="s">
+        <v>2378</v>
+      </c>
+    </row>
+    <row r="480" spans="4:4">
+      <c r="D480" s="21" t="s">
+        <v>2373</v>
+      </c>
+    </row>
+    <row r="481" spans="4:4">
+      <c r="D481" s="21" t="s">
+        <v>2374</v>
+      </c>
+    </row>
+    <row r="482" spans="4:4">
+      <c r="D482" s="21" t="s">
+        <v>2375</v>
+      </c>
+    </row>
+    <row r="483" spans="4:4">
+      <c r="D483" s="5"/>
+    </row>
+    <row r="484" spans="4:4">
+      <c r="D484" s="5"/>
+    </row>
+    <row r="485" spans="4:4">
+      <c r="D485" s="5"/>
+    </row>
+    <row r="486" spans="4:4" ht="17.25">
+      <c r="D486" s="157" t="s">
+        <v>2376</v>
+      </c>
+    </row>
+    <row r="487" spans="4:4">
+      <c r="D487" s="7" t="s">
+        <v>2377</v>
+      </c>
+    </row>
+    <row r="489" spans="4:4">
+      <c r="D489" t="s">
+        <v>2379</v>
+      </c>
+    </row>
+    <row r="490" spans="4:4">
+      <c r="D490" t="s">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="491" spans="4:4">
+      <c r="D491" t="s">
+        <v>2381</v>
+      </c>
+    </row>
+    <row r="492" spans="4:4">
+      <c r="D492" t="s">
+        <v>2382</v>
+      </c>
+    </row>
+    <row r="493" spans="4:4">
+      <c r="D493" t="s">
+        <v>2383</v>
+      </c>
+    </row>
+    <row r="495" spans="4:4">
+      <c r="D495" s="7" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="497" spans="4:4">
+      <c r="D497" t="s">
+        <v>2385</v>
+      </c>
+    </row>
+    <row r="498" spans="4:4">
+      <c r="D498" t="s">
+        <v>2386</v>
+      </c>
+    </row>
+    <row r="499" spans="4:4">
+      <c r="D499" t="s">
+        <v>2387</v>
+      </c>
+    </row>
+    <row r="500" spans="4:4">
+      <c r="D500" t="s">
+        <v>2388</v>
+      </c>
+    </row>
+    <row r="502" spans="4:4">
+      <c r="D502" s="7" t="s">
+        <v>2389</v>
+      </c>
+    </row>
+    <row r="504" spans="4:4">
+      <c r="D504" t="s">
+        <v>2390</v>
+      </c>
+    </row>
+    <row r="505" spans="4:4">
+      <c r="D505" t="s">
+        <v>2391</v>
+      </c>
+    </row>
+    <row r="506" spans="4:4">
+      <c r="D506" t="s">
+        <v>2392</v>
+      </c>
+    </row>
+    <row r="507" spans="4:4">
+      <c r="D507" t="s">
+        <v>2393</v>
+      </c>
+    </row>
+    <row r="508" spans="4:4">
+      <c r="D508" t="s">
+        <v>2394</v>
+      </c>
+    </row>
+    <row r="510" spans="4:4">
+      <c r="D510" s="7" t="s">
+        <v>2395</v>
+      </c>
+    </row>
+    <row r="512" spans="4:4">
+      <c r="D512" t="s">
+        <v>2396</v>
+      </c>
+    </row>
+    <row r="513" spans="4:4">
+      <c r="D513" t="s">
+        <v>2397</v>
+      </c>
+    </row>
+    <row r="514" spans="4:4">
+      <c r="D514" t="s">
+        <v>2398</v>
+      </c>
+    </row>
+    <row r="515" spans="4:4">
+      <c r="D515" t="s">
+        <v>2399</v>
+      </c>
+    </row>
+    <row r="517" spans="4:4" ht="17.25">
+      <c r="D517" s="157" t="s">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="518" spans="4:4">
+      <c r="D518" s="7" t="s">
+        <v>2401</v>
+      </c>
+    </row>
+    <row r="519" spans="4:4">
+      <c r="D519" s="20"/>
+    </row>
+    <row r="520" spans="4:4">
+      <c r="D520" s="22" t="s">
+        <v>2406</v>
+      </c>
+    </row>
+    <row r="521" spans="4:4">
+      <c r="D521" s="22" t="s">
+        <v>2407</v>
+      </c>
+    </row>
+    <row r="522" spans="4:4">
+      <c r="D522" s="22" t="s">
+        <v>2408</v>
+      </c>
+    </row>
+    <row r="523" spans="4:4">
+      <c r="D523" s="22" t="s">
+        <v>2409</v>
+      </c>
+    </row>
+    <row r="524" spans="4:4">
+      <c r="D524" s="22" t="s">
+        <v>2410</v>
+      </c>
+    </row>
+    <row r="525" spans="4:4">
+      <c r="D525" s="5"/>
+    </row>
+    <row r="526" spans="4:4">
+      <c r="D526" s="7" t="s">
+        <v>2402</v>
+      </c>
+    </row>
+    <row r="527" spans="4:4">
+      <c r="D527" s="20"/>
+    </row>
+    <row r="528" spans="4:4">
+      <c r="D528" s="25" t="s">
+        <v>2403</v>
+      </c>
+    </row>
+    <row r="529" spans="4:4">
+      <c r="D529" s="22" t="s">
+        <v>2411</v>
+      </c>
+    </row>
+    <row r="530" spans="4:4">
+      <c r="D530" s="22" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="531" spans="4:4">
+      <c r="D531" s="22" t="s">
+        <v>2413</v>
+      </c>
+    </row>
+    <row r="532" spans="4:4">
+      <c r="D532" s="22" t="s">
+        <v>2414</v>
+      </c>
+    </row>
+    <row r="533" spans="4:4">
+      <c r="D533" s="22" t="s">
+        <v>2415</v>
+      </c>
+    </row>
+    <row r="534" spans="4:4">
+      <c r="D534" s="22" t="s">
+        <v>2416</v>
+      </c>
+    </row>
+    <row r="535" spans="4:4">
+      <c r="D535" s="22" t="s">
+        <v>2417</v>
+      </c>
+    </row>
+    <row r="536" spans="4:4">
+      <c r="D536" s="22" t="s">
+        <v>2418</v>
+      </c>
+    </row>
+    <row r="537" spans="4:4">
+      <c r="D537" s="22" t="s">
+        <v>2419</v>
+      </c>
+    </row>
+    <row r="538" spans="4:4">
+      <c r="D538" s="22" t="s">
+        <v>2420</v>
+      </c>
+    </row>
+    <row r="539" spans="4:4">
+      <c r="D539" s="22" t="s">
+        <v>2421</v>
+      </c>
+    </row>
+    <row r="540" spans="4:4">
+      <c r="D540" s="22" t="s">
+        <v>2422</v>
+      </c>
+    </row>
+    <row r="541" spans="4:4">
+      <c r="D541" s="22" t="s">
+        <v>2423</v>
+      </c>
+    </row>
+    <row r="542" spans="4:4">
+      <c r="D542" s="22" t="s">
+        <v>2424</v>
+      </c>
+    </row>
+    <row r="543" spans="4:4">
+      <c r="D543" s="5"/>
+    </row>
+    <row r="544" spans="4:4">
+      <c r="D544" s="7" t="s">
+        <v>2404</v>
+      </c>
+    </row>
+    <row r="545" spans="4:4">
+      <c r="D545" s="20"/>
+    </row>
+    <row r="546" spans="4:4">
+      <c r="D546" s="22" t="s">
+        <v>2425</v>
+      </c>
+    </row>
+    <row r="547" spans="4:4">
+      <c r="D547" s="22" t="s">
+        <v>2426</v>
+      </c>
+    </row>
+    <row r="548" spans="4:4">
+      <c r="D548" s="22" t="s">
+        <v>2427</v>
+      </c>
+    </row>
+    <row r="549" spans="4:4">
+      <c r="D549" s="5"/>
+    </row>
+    <row r="550" spans="4:4">
+      <c r="D550" s="7" t="s">
+        <v>2405</v>
+      </c>
+    </row>
+    <row r="552" spans="4:4">
+      <c r="D552" t="s">
+        <v>2428</v>
+      </c>
+    </row>
+    <row r="554" spans="4:4">
+      <c r="D554" t="s">
+        <v>2429</v>
+      </c>
+    </row>
+    <row r="555" spans="4:4">
+      <c r="D555" t="s">
+        <v>2430</v>
+      </c>
+    </row>
+    <row r="556" spans="4:4">
+      <c r="D556" t="s">
+        <v>2431</v>
+      </c>
+    </row>
+    <row r="557" spans="4:4">
+      <c r="D557" t="s">
+        <v>2432</v>
+      </c>
+    </row>
+    <row r="558" spans="4:4">
+      <c r="D558" t="s">
+        <v>2433</v>
+      </c>
+    </row>
+    <row r="559" spans="4:4">
+      <c r="D559" t="s">
+        <v>2434</v>
+      </c>
+    </row>
+    <row r="560" spans="4:4">
+      <c r="D560" t="s">
+        <v>2435</v>
+      </c>
+    </row>
+    <row r="562" spans="4:4">
+      <c r="D562" t="s">
+        <v>2436</v>
+      </c>
+    </row>
+    <row r="563" spans="4:4">
+      <c r="D563" t="s">
+        <v>2437</v>
+      </c>
+    </row>
+    <row r="565" spans="4:4">
+      <c r="D565" s="4" t="s">
+        <v>2438</v>
+      </c>
+    </row>
+    <row r="566" spans="4:4">
+      <c r="D566" s="10" t="s">
+        <v>2439</v>
+      </c>
+    </row>
+    <row r="567" spans="4:4">
+      <c r="D567" s="10" t="s">
+        <v>2440</v>
+      </c>
+    </row>
+    <row r="568" spans="4:4">
+      <c r="D568" s="10" t="s">
+        <v>2441</v>
+      </c>
+    </row>
+    <row r="569" spans="4:4">
+      <c r="D569" s="10" t="s">
+        <v>2442</v>
+      </c>
+    </row>
+    <row r="570" spans="4:4">
+      <c r="D570" s="14" t="s">
+        <v>2443</v>
+      </c>
+    </row>
+    <row r="571" spans="4:4">
+      <c r="D571" s="10" t="s">
+        <v>2444</v>
+      </c>
+    </row>
+    <row r="572" spans="4:4">
+      <c r="D572" s="10" t="s">
+        <v>2445</v>
+      </c>
+    </row>
+    <row r="574" spans="4:4">
+      <c r="D574" s="8" t="s">
+        <v>2461</v>
+      </c>
+    </row>
+    <row r="575" spans="4:4" ht="17.25">
+      <c r="D575" s="158" t="s">
+        <v>2446</v>
+      </c>
+    </row>
+    <row r="576" spans="4:4">
+      <c r="D576" s="183" t="s">
+        <v>2462</v>
+      </c>
+    </row>
+    <row r="577" spans="4:4">
+      <c r="D577" s="7" t="s">
+        <v>2447</v>
+      </c>
+    </row>
+    <row r="578" spans="4:4">
+      <c r="D578" s="20"/>
+    </row>
+    <row r="579" spans="4:4">
+      <c r="D579" s="21" t="s">
+        <v>2448</v>
+      </c>
+    </row>
+    <row r="580" spans="4:4">
+      <c r="D580" s="21" t="s">
+        <v>2449</v>
+      </c>
+    </row>
+    <row r="581" spans="4:4">
+      <c r="D581" s="21" t="s">
+        <v>2450</v>
+      </c>
+    </row>
+    <row r="582" spans="4:4">
+      <c r="D582" s="21" t="s">
+        <v>2451</v>
+      </c>
+    </row>
+    <row r="583" spans="4:4">
+      <c r="D583" s="5"/>
+    </row>
+    <row r="584" spans="4:4" ht="17.25">
+      <c r="D584" s="158" t="s">
+        <v>2452</v>
+      </c>
+    </row>
+    <row r="585" spans="4:4">
+      <c r="D585" s="16" t="s">
+        <v>2453</v>
+      </c>
+    </row>
+    <row r="586" spans="4:4">
+      <c r="D586" s="7" t="s">
+        <v>2447</v>
+      </c>
+    </row>
+    <row r="587" spans="4:4">
+      <c r="D587" s="20"/>
+    </row>
+    <row r="588" spans="4:4">
+      <c r="D588" s="21" t="s">
+        <v>2454</v>
+      </c>
+    </row>
+    <row r="589" spans="4:4">
+      <c r="D589" s="21" t="s">
+        <v>2455</v>
+      </c>
+    </row>
+    <row r="590" spans="4:4">
+      <c r="D590" s="21" t="s">
+        <v>2456</v>
+      </c>
+    </row>
+    <row r="591" spans="4:4">
+      <c r="D591" s="21" t="s">
+        <v>2457</v>
+      </c>
+    </row>
+    <row r="592" spans="4:4">
+      <c r="D592" s="5"/>
+    </row>
+    <row r="593" spans="4:4" ht="17.25">
+      <c r="D593" s="158" t="s">
+        <v>2458</v>
+      </c>
+    </row>
+    <row r="594" spans="4:4">
+      <c r="D594" s="7" t="s">
+        <v>2459</v>
+      </c>
+    </row>
+    <row r="595" spans="4:4">
+      <c r="D595" s="20"/>
+    </row>
+    <row r="596" spans="4:4">
+      <c r="D596" s="184" t="s">
+        <v>2463</v>
+      </c>
+    </row>
+    <row r="597" spans="4:4">
+      <c r="D597" s="25" t="s">
+        <v>2460</v>
+      </c>
+    </row>
+    <row r="599" spans="4:4">
+      <c r="D599" t="s">
+        <v>2464</v>
+      </c>
+    </row>
+    <row r="600" spans="4:4">
+      <c r="D600" t="s">
+        <v>2465</v>
+      </c>
+    </row>
+    <row r="601" spans="4:4">
+      <c r="D601" t="s">
+        <v>2466</v>
+      </c>
+    </row>
+    <row r="602" spans="4:4">
+      <c r="D602" t="s">
+        <v>2467</v>
+      </c>
+    </row>
+    <row r="603" spans="4:4">
+      <c r="D603" t="s">
+        <v>2468</v>
+      </c>
+    </row>
+    <row r="604" spans="4:4">
+      <c r="D604" t="s">
+        <v>2469</v>
+      </c>
+    </row>
+    <row r="605" spans="4:4">
+      <c r="D605" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="606" spans="4:4">
+      <c r="D606" t="s">
+        <v>2471</v>
+      </c>
+    </row>
+    <row r="608" spans="4:4">
+      <c r="D608" s="7" t="s">
+        <v>2472</v>
+      </c>
+    </row>
+    <row r="609" spans="4:4">
+      <c r="D609" s="20"/>
+    </row>
+    <row r="610" spans="4:4">
+      <c r="D610" s="25" t="s">
+        <v>2473</v>
+      </c>
+    </row>
+    <row r="612" spans="4:4">
+      <c r="D612" t="s">
+        <v>2474</v>
+      </c>
+    </row>
+    <row r="614" spans="4:4">
+      <c r="D614" s="21" t="s">
+        <v>2479</v>
+      </c>
+    </row>
+    <row r="615" spans="4:4">
+      <c r="D615" s="5"/>
+    </row>
+    <row r="616" spans="4:4">
+      <c r="D616" s="7" t="s">
+        <v>2475</v>
+      </c>
+    </row>
+    <row r="617" spans="4:4">
+      <c r="D617" s="20"/>
+    </row>
+    <row r="618" spans="4:4">
+      <c r="D618" s="25" t="s">
+        <v>2476</v>
+      </c>
+    </row>
+    <row r="619" spans="4:4">
+      <c r="D619" s="21" t="s">
+        <v>2477</v>
+      </c>
+    </row>
+    <row r="620" spans="4:4">
+      <c r="D620" s="5"/>
+    </row>
+    <row r="621" spans="4:4">
+      <c r="D621" s="5"/>
+    </row>
+    <row r="622" spans="4:4">
+      <c r="D622" s="5"/>
+    </row>
+    <row r="623" spans="4:4" ht="30">
+      <c r="D623" s="16" t="s">
+        <v>2478</v>
+      </c>
+    </row>
+    <row r="624" spans="4:4">
+      <c r="D624" s="8" t="s">
+        <v>2480</v>
+      </c>
+    </row>
+    <row r="626" spans="4:4">
+      <c r="D626" s="16" t="s">
+        <v>2481</v>
+      </c>
+    </row>
+    <row r="627" spans="4:4">
+      <c r="D627" s="8" t="s">
+        <v>2482</v>
+      </c>
+    </row>
+    <row r="628" spans="4:4">
+      <c r="D628" s="20"/>
+    </row>
+    <row r="629" spans="4:4">
+      <c r="D629" s="22" t="s">
+        <v>2485</v>
+      </c>
+    </row>
+    <row r="630" spans="4:4">
+      <c r="D630" s="22" t="s">
+        <v>2486</v>
+      </c>
+    </row>
+    <row r="631" spans="4:4">
+      <c r="D631" s="163" t="s">
+        <v>2487</v>
+      </c>
+    </row>
+    <row r="632" spans="4:4">
+      <c r="D632" s="22" t="s">
+        <v>2488</v>
+      </c>
+    </row>
+    <row r="633" spans="4:4">
+      <c r="D633" s="22" t="s">
+        <v>2489</v>
+      </c>
+    </row>
+    <row r="634" spans="4:4">
+      <c r="D634" s="25" t="s">
+        <v>2483</v>
+      </c>
+    </row>
+    <row r="635" spans="4:4">
+      <c r="D635" s="22" t="s">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="636" spans="4:4">
+      <c r="D636" s="22" t="s">
+        <v>2491</v>
+      </c>
+    </row>
+    <row r="637" spans="4:4">
+      <c r="D637" s="5"/>
+    </row>
+    <row r="638" spans="4:4">
+      <c r="D638" s="8" t="s">
+        <v>2484</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D5" r:id="rId1" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="F18" r:id="rId2" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="F19" r:id="rId3" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="F20" r:id="rId4" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="F21" r:id="rId5" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="F25" r:id="rId6" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D29" r:id="rId7" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D31" r:id="rId8" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D33" r:id="rId9" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="F41" r:id="rId10" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="F42" r:id="rId11" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="F45" r:id="rId12" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="F46" r:id="rId13" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="F48" r:id="rId14" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="F49" r:id="rId15" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D50" r:id="rId16" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="F60" r:id="rId17" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="F61" r:id="rId18" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="F62" r:id="rId19" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="F63" r:id="rId20" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="F64" r:id="rId21" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="F65" r:id="rId22" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="F66" r:id="rId23" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="F67" r:id="rId24" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="F68" r:id="rId25" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="F69" r:id="rId26" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="F71" r:id="rId27" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D72" r:id="rId28" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D84" r:id="rId29" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D85" r:id="rId30" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D86" r:id="rId31" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D87" r:id="rId32" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D88" r:id="rId33" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D101" r:id="rId34" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D107" r:id="rId35" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D108" r:id="rId36" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D109" r:id="rId37" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D110" r:id="rId38" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D116" r:id="rId39" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D118" r:id="rId40" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D119" r:id="rId41" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D120" r:id="rId42" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D121" r:id="rId43" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D126" r:id="rId44" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D128" r:id="rId45" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D134" r:id="rId46" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D173" r:id="rId47" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D176" r:id="rId48" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D254" r:id="rId49" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D267" r:id="rId50" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D268" r:id="rId51" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D273" r:id="rId52" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D280" r:id="rId53" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D285" r:id="rId54" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D298" r:id="rId55" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D309" r:id="rId56" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D313" r:id="rId57" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D440" r:id="rId58" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D455" r:id="rId59" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D457" r:id="rId60" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D470" r:id="rId61" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D477" r:id="rId62" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D528" r:id="rId63" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D570" r:id="rId64" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D585" r:id="rId65" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D597" r:id="rId66" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D610" r:id="rId67" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D618" r:id="rId68" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D623" r:id="rId69" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D626" r:id="rId70" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+    <hyperlink ref="D634" r:id="rId71" display="vscode-file://vscode-app/c:/Users/tmsjd/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId72"/>
+  <controls>
+    <control shapeId="6180" r:id="rId73" name="Control 36"/>
+    <control shapeId="6179" r:id="rId74" name="Control 35"/>
+    <control shapeId="6178" r:id="rId75" name="Control 34"/>
+    <control shapeId="6177" r:id="rId76" name="Control 33"/>
+    <control shapeId="6176" r:id="rId77" name="Control 32"/>
+    <control shapeId="6175" r:id="rId78" name="Control 31"/>
+    <control shapeId="6174" r:id="rId79" name="Control 30"/>
+    <control shapeId="6173" r:id="rId80" name="Control 29"/>
+    <control shapeId="6172" r:id="rId81" name="Control 28"/>
+    <control shapeId="6171" r:id="rId82" name="Control 27"/>
+    <control shapeId="6170" r:id="rId83" name="Control 26"/>
+    <control shapeId="6169" r:id="rId84" name="Control 25"/>
+    <control shapeId="6168" r:id="rId85" name="Control 24"/>
+    <control shapeId="6167" r:id="rId86" name="Control 23"/>
+    <control shapeId="6166" r:id="rId87" name="Control 22"/>
+    <control shapeId="6165" r:id="rId88" name="Control 21"/>
+    <control shapeId="6164" r:id="rId89" name="Control 20"/>
+    <control shapeId="6163" r:id="rId90" name="Control 19"/>
+    <control shapeId="6162" r:id="rId91" name="Control 18"/>
+    <control shapeId="6161" r:id="rId92" name="Control 17"/>
+    <control shapeId="6160" r:id="rId93" name="Control 16"/>
+    <control shapeId="6159" r:id="rId94" name="Control 15"/>
+    <control shapeId="6158" r:id="rId95" name="Control 14"/>
+    <control shapeId="6157" r:id="rId96" name="Control 13"/>
+    <control shapeId="6156" r:id="rId97" name="Control 12"/>
+    <control shapeId="6155" r:id="rId98" name="Control 11"/>
+    <control shapeId="6154" r:id="rId99" name="Control 10"/>
+    <control shapeId="6153" r:id="rId100" name="Control 9"/>
+    <control shapeId="6152" r:id="rId101" name="Control 8"/>
+    <control shapeId="6151" r:id="rId102" name="Control 7"/>
+    <control shapeId="6150" r:id="rId103" name="Control 6"/>
+    <control shapeId="6149" r:id="rId104" name="Control 5"/>
+  </controls>
+</worksheet>
 </file>